--- a/excel/5000(n)/RAW_Dataset.xlsx
+++ b/excel/5000(n)/RAW_Dataset.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\#Java-Practice\##SS2\Lab3 Sorting\excel\"/>
     </mc:Choice>
@@ -17,7 +17,7 @@
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
   </extLst>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="112">
   <si>
     <t xml:space="preserve">Algorithm </t>
   </si>
@@ -58,12 +58,316 @@
   </si>
   <si>
     <t>Trial 9</t>
+  </si>
+  <si>
+    <t>Bubble Sort</t>
+  </si>
+  <si>
+    <t>Bubble Sort (Reverse)</t>
+  </si>
+  <si>
+    <t>Insertion Sort</t>
+  </si>
+  <si>
+    <t>Insertion Sort (Reverse)</t>
+  </si>
+  <si>
+    <t>Selection Sort</t>
+  </si>
+  <si>
+    <t>Selection Sort (Reverse)</t>
+  </si>
+  <si>
+    <t>Merge Sort</t>
+  </si>
+  <si>
+    <t>Merge Sort (Reverse)</t>
+  </si>
+  <si>
+    <t>Quick Sort</t>
+  </si>
+  <si>
+    <t>Quick Sort (Reverse)</t>
+  </si>
+  <si>
+    <t>Trial 10</t>
+  </si>
+  <si>
+    <t>Trial 11</t>
+  </si>
+  <si>
+    <t>Trial 12</t>
+  </si>
+  <si>
+    <t>Trial 13</t>
+  </si>
+  <si>
+    <t>Trial 14</t>
+  </si>
+  <si>
+    <t>Trial 15</t>
+  </si>
+  <si>
+    <t>Trial 16</t>
+  </si>
+  <si>
+    <t>Trial 17</t>
+  </si>
+  <si>
+    <t>Trial 18</t>
+  </si>
+  <si>
+    <t>Trial 19</t>
+  </si>
+  <si>
+    <t>Trial 20</t>
+  </si>
+  <si>
+    <t>Trial 21</t>
+  </si>
+  <si>
+    <t>Trial 22</t>
+  </si>
+  <si>
+    <t>Trial 23</t>
+  </si>
+  <si>
+    <t>Trial 24</t>
+  </si>
+  <si>
+    <t>Trial 25</t>
+  </si>
+  <si>
+    <t>Trial 26</t>
+  </si>
+  <si>
+    <t>Trial 27</t>
+  </si>
+  <si>
+    <t>Trial 28</t>
+  </si>
+  <si>
+    <t>Trial 29</t>
+  </si>
+  <si>
+    <t>Trial 30</t>
+  </si>
+  <si>
+    <t>Trial 31</t>
+  </si>
+  <si>
+    <t>Trial 32</t>
+  </si>
+  <si>
+    <t>Trial 33</t>
+  </si>
+  <si>
+    <t>Trial 34</t>
+  </si>
+  <si>
+    <t>Trial 35</t>
+  </si>
+  <si>
+    <t>Trial 36</t>
+  </si>
+  <si>
+    <t>Trial 37</t>
+  </si>
+  <si>
+    <t>Trial 38</t>
+  </si>
+  <si>
+    <t>Trial 39</t>
+  </si>
+  <si>
+    <t>Trial 40</t>
+  </si>
+  <si>
+    <t>Trial 41</t>
+  </si>
+  <si>
+    <t>Trial 42</t>
+  </si>
+  <si>
+    <t>Trial 43</t>
+  </si>
+  <si>
+    <t>Trial 44</t>
+  </si>
+  <si>
+    <t>Trial 45</t>
+  </si>
+  <si>
+    <t>Trial 46</t>
+  </si>
+  <si>
+    <t>Trial 47</t>
+  </si>
+  <si>
+    <t>Trial 48</t>
+  </si>
+  <si>
+    <t>Trial 49</t>
+  </si>
+  <si>
+    <t>Trial 50</t>
+  </si>
+  <si>
+    <t>Trial 51</t>
+  </si>
+  <si>
+    <t>Trial 52</t>
+  </si>
+  <si>
+    <t>Trial 53</t>
+  </si>
+  <si>
+    <t>Trial 54</t>
+  </si>
+  <si>
+    <t>Trial 55</t>
+  </si>
+  <si>
+    <t>Trial 56</t>
+  </si>
+  <si>
+    <t>Trial 57</t>
+  </si>
+  <si>
+    <t>Trial 58</t>
+  </si>
+  <si>
+    <t>Trial 59</t>
+  </si>
+  <si>
+    <t>Trial 60</t>
+  </si>
+  <si>
+    <t>Trial 61</t>
+  </si>
+  <si>
+    <t>Trial 62</t>
+  </si>
+  <si>
+    <t>Trial 63</t>
+  </si>
+  <si>
+    <t>Trial 64</t>
+  </si>
+  <si>
+    <t>Trial 65</t>
+  </si>
+  <si>
+    <t>Trial 66</t>
+  </si>
+  <si>
+    <t>Trial 67</t>
+  </si>
+  <si>
+    <t>Trial 68</t>
+  </si>
+  <si>
+    <t>Trial 69</t>
+  </si>
+  <si>
+    <t>Trial 70</t>
+  </si>
+  <si>
+    <t>Trial 71</t>
+  </si>
+  <si>
+    <t>Trial 72</t>
+  </si>
+  <si>
+    <t>Trial 73</t>
+  </si>
+  <si>
+    <t>Trial 74</t>
+  </si>
+  <si>
+    <t>Trial 75</t>
+  </si>
+  <si>
+    <t>Trial 76</t>
+  </si>
+  <si>
+    <t>Trial 77</t>
+  </si>
+  <si>
+    <t>Trial 78</t>
+  </si>
+  <si>
+    <t>Trial 79</t>
+  </si>
+  <si>
+    <t>Trial 80</t>
+  </si>
+  <si>
+    <t>Trial 81</t>
+  </si>
+  <si>
+    <t>Trial 82</t>
+  </si>
+  <si>
+    <t>Trial 83</t>
+  </si>
+  <si>
+    <t>Trial 84</t>
+  </si>
+  <si>
+    <t>Trial 85</t>
+  </si>
+  <si>
+    <t>Trial 86</t>
+  </si>
+  <si>
+    <t>Trial 87</t>
+  </si>
+  <si>
+    <t>Trial 88</t>
+  </si>
+  <si>
+    <t>Trial 89</t>
+  </si>
+  <si>
+    <t>Trial 90</t>
+  </si>
+  <si>
+    <t>Trial 91</t>
+  </si>
+  <si>
+    <t>Trial 92</t>
+  </si>
+  <si>
+    <t>Trial 93</t>
+  </si>
+  <si>
+    <t>Trial 94</t>
+  </si>
+  <si>
+    <t>Trial 95</t>
+  </si>
+  <si>
+    <t>Trial 96</t>
+  </si>
+  <si>
+    <t>Trial 97</t>
+  </si>
+  <si>
+    <t>Trial 98</t>
+  </si>
+  <si>
+    <t>Trial 99</t>
+  </si>
+  <si>
+    <t>Trial 100</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -388,11 +692,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K1"/>
+  <dimension ref="A1:CX11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.77734375" customWidth="1"/>
-    <col min="2" max="2" width="13.33203125" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="14.77734375"/>
+    <col min="2" max="2" customWidth="true" width="13.33203125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.5">
@@ -402,32 +706,3385 @@
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" t="s" s="0">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" t="s" s="0">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" t="s" s="0">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" t="s" s="0">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" t="s" s="0">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" t="s" s="0">
         <v>10</v>
+      </c>
+      <c r="L1" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="M1" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="N1" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="O1" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="P1" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="Q1" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="R1" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="S1" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="T1" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="U1" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="V1" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="W1" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="X1" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="Y1" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="Z1" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="AA1" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="AB1" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="AC1" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="AD1" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="AE1" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="AF1" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="AG1" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="AH1" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="AI1" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="AJ1" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="AK1" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="AL1" t="s" s="0">
+        <v>47</v>
+      </c>
+      <c r="AM1" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="AN1" t="s" s="0">
+        <v>49</v>
+      </c>
+      <c r="AO1" t="s" s="0">
+        <v>50</v>
+      </c>
+      <c r="AP1" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="AQ1" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="AR1" t="s" s="0">
+        <v>53</v>
+      </c>
+      <c r="AS1" t="s" s="0">
+        <v>54</v>
+      </c>
+      <c r="AT1" t="s" s="0">
+        <v>55</v>
+      </c>
+      <c r="AU1" t="s" s="0">
+        <v>56</v>
+      </c>
+      <c r="AV1" t="s" s="0">
+        <v>57</v>
+      </c>
+      <c r="AW1" t="s" s="0">
+        <v>58</v>
+      </c>
+      <c r="AX1" t="s" s="0">
+        <v>59</v>
+      </c>
+      <c r="AY1" t="s" s="0">
+        <v>60</v>
+      </c>
+      <c r="AZ1" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="BA1" t="s" s="0">
+        <v>62</v>
+      </c>
+      <c r="BB1" t="s" s="0">
+        <v>63</v>
+      </c>
+      <c r="BC1" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="BD1" t="s" s="0">
+        <v>65</v>
+      </c>
+      <c r="BE1" t="s" s="0">
+        <v>66</v>
+      </c>
+      <c r="BF1" t="s" s="0">
+        <v>67</v>
+      </c>
+      <c r="BG1" t="s" s="0">
+        <v>68</v>
+      </c>
+      <c r="BH1" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="BI1" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="BJ1" t="s" s="0">
+        <v>71</v>
+      </c>
+      <c r="BK1" t="s" s="0">
+        <v>72</v>
+      </c>
+      <c r="BL1" t="s" s="0">
+        <v>73</v>
+      </c>
+      <c r="BM1" t="s" s="0">
+        <v>74</v>
+      </c>
+      <c r="BN1" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="BO1" t="s" s="0">
+        <v>76</v>
+      </c>
+      <c r="BP1" t="s" s="0">
+        <v>77</v>
+      </c>
+      <c r="BQ1" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="BR1" t="s" s="0">
+        <v>79</v>
+      </c>
+      <c r="BS1" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="BT1" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="BU1" t="s" s="0">
+        <v>82</v>
+      </c>
+      <c r="BV1" t="s" s="0">
+        <v>83</v>
+      </c>
+      <c r="BW1" t="s" s="0">
+        <v>84</v>
+      </c>
+      <c r="BX1" t="s" s="0">
+        <v>85</v>
+      </c>
+      <c r="BY1" t="s" s="0">
+        <v>86</v>
+      </c>
+      <c r="BZ1" t="s" s="0">
+        <v>87</v>
+      </c>
+      <c r="CA1" t="s" s="0">
+        <v>88</v>
+      </c>
+      <c r="CB1" t="s" s="0">
+        <v>89</v>
+      </c>
+      <c r="CC1" t="s" s="0">
+        <v>90</v>
+      </c>
+      <c r="CD1" t="s" s="0">
+        <v>91</v>
+      </c>
+      <c r="CE1" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="CF1" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="CG1" t="s" s="0">
+        <v>94</v>
+      </c>
+      <c r="CH1" t="s" s="0">
+        <v>95</v>
+      </c>
+      <c r="CI1" t="s" s="0">
+        <v>96</v>
+      </c>
+      <c r="CJ1" t="s" s="0">
+        <v>97</v>
+      </c>
+      <c r="CK1" t="s" s="0">
+        <v>98</v>
+      </c>
+      <c r="CL1" t="s" s="0">
+        <v>99</v>
+      </c>
+      <c r="CM1" t="s" s="0">
+        <v>100</v>
+      </c>
+      <c r="CN1" t="s" s="0">
+        <v>101</v>
+      </c>
+      <c r="CO1" t="s" s="0">
+        <v>102</v>
+      </c>
+      <c r="CP1" t="s" s="0">
+        <v>103</v>
+      </c>
+      <c r="CQ1" t="s" s="0">
+        <v>104</v>
+      </c>
+      <c r="CR1" t="s" s="0">
+        <v>105</v>
+      </c>
+      <c r="CS1" t="s" s="0">
+        <v>106</v>
+      </c>
+      <c r="CT1" t="s" s="0">
+        <v>107</v>
+      </c>
+      <c r="CU1" t="s" s="0">
+        <v>108</v>
+      </c>
+      <c r="CV1" t="s" s="0">
+        <v>109</v>
+      </c>
+      <c r="CW1" t="s" s="0">
+        <v>110</v>
+      </c>
+      <c r="CX1" t="s" s="0">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="B2" t="n" s="0">
+        <v>5000.0</v>
+      </c>
+      <c r="C2" t="n" s="0">
+        <v>1.51447E7</v>
+      </c>
+      <c r="D2" t="n" s="0">
+        <v>1.19511E7</v>
+      </c>
+      <c r="E2" t="n" s="0">
+        <v>1.21762E7</v>
+      </c>
+      <c r="F2" t="n" s="0">
+        <v>1.11191E7</v>
+      </c>
+      <c r="G2" t="n" s="0">
+        <v>1.10616E7</v>
+      </c>
+      <c r="H2" t="n" s="0">
+        <v>1.13021E7</v>
+      </c>
+      <c r="I2" t="n" s="0">
+        <v>1.07964E7</v>
+      </c>
+      <c r="J2" t="n" s="0">
+        <v>1.15879E7</v>
+      </c>
+      <c r="K2" t="n" s="0">
+        <v>1.22439E7</v>
+      </c>
+      <c r="L2" t="n" s="0">
+        <v>1.78299E7</v>
+      </c>
+      <c r="M2" t="n" s="0">
+        <v>1.86698E7</v>
+      </c>
+      <c r="N2" t="n" s="0">
+        <v>1.76574E7</v>
+      </c>
+      <c r="O2" t="n" s="0">
+        <v>1.68903E7</v>
+      </c>
+      <c r="P2" t="n" s="0">
+        <v>1.85896E7</v>
+      </c>
+      <c r="Q2" t="n" s="0">
+        <v>1.76104E7</v>
+      </c>
+      <c r="R2" t="n" s="0">
+        <v>1.82474E7</v>
+      </c>
+      <c r="S2" t="n" s="0">
+        <v>1.82568E7</v>
+      </c>
+      <c r="T2" t="n" s="0">
+        <v>1.79162E7</v>
+      </c>
+      <c r="U2" t="n" s="0">
+        <v>1.77377E7</v>
+      </c>
+      <c r="V2" t="n" s="0">
+        <v>1.73216E7</v>
+      </c>
+      <c r="W2" t="n" s="0">
+        <v>1.7111E7</v>
+      </c>
+      <c r="X2" t="n" s="0">
+        <v>1.83537E7</v>
+      </c>
+      <c r="Y2" t="n" s="0">
+        <v>1.8104E7</v>
+      </c>
+      <c r="Z2" t="n" s="0">
+        <v>1.80698E7</v>
+      </c>
+      <c r="AA2" t="n" s="0">
+        <v>1.8413E7</v>
+      </c>
+      <c r="AB2" t="n" s="0">
+        <v>1.78889E7</v>
+      </c>
+      <c r="AC2" t="n" s="0">
+        <v>1.79818E7</v>
+      </c>
+      <c r="AD2" t="n" s="0">
+        <v>1.69383E7</v>
+      </c>
+      <c r="AE2" t="n" s="0">
+        <v>1.76985E7</v>
+      </c>
+      <c r="AF2" t="n" s="0">
+        <v>1.91289E7</v>
+      </c>
+      <c r="AG2" t="n" s="0">
+        <v>1.91334E7</v>
+      </c>
+      <c r="AH2" t="n" s="0">
+        <v>1.82842E7</v>
+      </c>
+      <c r="AI2" t="n" s="0">
+        <v>1.68072E7</v>
+      </c>
+      <c r="AJ2" t="n" s="0">
+        <v>1.79217E7</v>
+      </c>
+      <c r="AK2" t="n" s="0">
+        <v>1.70116E7</v>
+      </c>
+      <c r="AL2" t="n" s="0">
+        <v>1.70961E7</v>
+      </c>
+      <c r="AM2" t="n" s="0">
+        <v>1.79864E7</v>
+      </c>
+      <c r="AN2" t="n" s="0">
+        <v>1.68838E7</v>
+      </c>
+      <c r="AO2" t="n" s="0">
+        <v>1.85026E7</v>
+      </c>
+      <c r="AP2" t="n" s="0">
+        <v>1.79882E7</v>
+      </c>
+      <c r="AQ2" t="n" s="0">
+        <v>1.87335E7</v>
+      </c>
+      <c r="AR2" t="n" s="0">
+        <v>1.77753E7</v>
+      </c>
+      <c r="AS2" t="n" s="0">
+        <v>2.04716E7</v>
+      </c>
+      <c r="AT2" t="n" s="0">
+        <v>1.71476E7</v>
+      </c>
+      <c r="AU2" t="n" s="0">
+        <v>1.67475E7</v>
+      </c>
+      <c r="AV2" t="n" s="0">
+        <v>1.81135E7</v>
+      </c>
+      <c r="AW2" t="n" s="0">
+        <v>1.81907E7</v>
+      </c>
+      <c r="AX2" t="n" s="0">
+        <v>1.73055E7</v>
+      </c>
+      <c r="AY2" t="n" s="0">
+        <v>1.73212E7</v>
+      </c>
+      <c r="AZ2" t="n" s="0">
+        <v>1.68879E7</v>
+      </c>
+      <c r="BA2" t="n" s="0">
+        <v>1.73966E7</v>
+      </c>
+      <c r="BB2" t="n" s="0">
+        <v>1.7144E7</v>
+      </c>
+      <c r="BC2" t="n" s="0">
+        <v>1.67994E7</v>
+      </c>
+      <c r="BD2" t="n" s="0">
+        <v>1.81124E7</v>
+      </c>
+      <c r="BE2" t="n" s="0">
+        <v>1.72418E7</v>
+      </c>
+      <c r="BF2" t="n" s="0">
+        <v>1.70798E7</v>
+      </c>
+      <c r="BG2" t="n" s="0">
+        <v>1.74839E7</v>
+      </c>
+      <c r="BH2" t="n" s="0">
+        <v>1.90238E7</v>
+      </c>
+      <c r="BI2" t="n" s="0">
+        <v>1.76631E7</v>
+      </c>
+      <c r="BJ2" t="n" s="0">
+        <v>1.72419E7</v>
+      </c>
+      <c r="BK2" t="n" s="0">
+        <v>1.69726E7</v>
+      </c>
+      <c r="BL2" t="n" s="0">
+        <v>1.70308E7</v>
+      </c>
+      <c r="BM2" t="n" s="0">
+        <v>1.70979E7</v>
+      </c>
+      <c r="BN2" t="n" s="0">
+        <v>1.83738E7</v>
+      </c>
+      <c r="BO2" t="n" s="0">
+        <v>1.74931E7</v>
+      </c>
+      <c r="BP2" t="n" s="0">
+        <v>1.78596E7</v>
+      </c>
+      <c r="BQ2" t="n" s="0">
+        <v>1.73445E7</v>
+      </c>
+      <c r="BR2" t="n" s="0">
+        <v>1.69846E7</v>
+      </c>
+      <c r="BS2" t="n" s="0">
+        <v>1.69671E7</v>
+      </c>
+      <c r="BT2" t="n" s="0">
+        <v>1.74381E7</v>
+      </c>
+      <c r="BU2" t="n" s="0">
+        <v>1.78257E7</v>
+      </c>
+      <c r="BV2" t="n" s="0">
+        <v>1.75819E7</v>
+      </c>
+      <c r="BW2" t="n" s="0">
+        <v>1.78771E7</v>
+      </c>
+      <c r="BX2" t="n" s="0">
+        <v>1.74936E7</v>
+      </c>
+      <c r="BY2" t="n" s="0">
+        <v>1.78592E7</v>
+      </c>
+      <c r="BZ2" t="n" s="0">
+        <v>1.95395E7</v>
+      </c>
+      <c r="CA2" t="n" s="0">
+        <v>1.88381E7</v>
+      </c>
+      <c r="CB2" t="n" s="0">
+        <v>2.05096E7</v>
+      </c>
+      <c r="CC2" t="n" s="0">
+        <v>1.79752E7</v>
+      </c>
+      <c r="CD2" t="n" s="0">
+        <v>1.83368E7</v>
+      </c>
+      <c r="CE2" t="n" s="0">
+        <v>1.82364E7</v>
+      </c>
+      <c r="CF2" t="n" s="0">
+        <v>1.80925E7</v>
+      </c>
+      <c r="CG2" t="n" s="0">
+        <v>1.68926E7</v>
+      </c>
+      <c r="CH2" t="n" s="0">
+        <v>1.72075E7</v>
+      </c>
+      <c r="CI2" t="n" s="0">
+        <v>1.7309E7</v>
+      </c>
+      <c r="CJ2" t="n" s="0">
+        <v>1.74768E7</v>
+      </c>
+      <c r="CK2" t="n" s="0">
+        <v>2.17182E7</v>
+      </c>
+      <c r="CL2" t="n" s="0">
+        <v>1.83938E7</v>
+      </c>
+      <c r="CM2" t="n" s="0">
+        <v>1.78497E7</v>
+      </c>
+      <c r="CN2" t="n" s="0">
+        <v>1.68161E7</v>
+      </c>
+      <c r="CO2" t="n" s="0">
+        <v>1.68023E7</v>
+      </c>
+      <c r="CP2" t="n" s="0">
+        <v>1.9027E7</v>
+      </c>
+      <c r="CQ2" t="n" s="0">
+        <v>1.81381E7</v>
+      </c>
+      <c r="CR2" t="n" s="0">
+        <v>1.79663E7</v>
+      </c>
+      <c r="CS2" t="n" s="0">
+        <v>1.81273E7</v>
+      </c>
+      <c r="CT2" t="n" s="0">
+        <v>1.81149E7</v>
+      </c>
+      <c r="CU2" t="n" s="0">
+        <v>1.82594E7</v>
+      </c>
+      <c r="CV2" t="n" s="0">
+        <v>1.80103E7</v>
+      </c>
+      <c r="CW2" t="n" s="0">
+        <v>1.81572E7</v>
+      </c>
+      <c r="CX2" t="n" s="0">
+        <v>1.83114E7</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="B3" t="n" s="0">
+        <v>5000.0</v>
+      </c>
+      <c r="C3" t="n" s="0">
+        <v>1.35179E7</v>
+      </c>
+      <c r="D3" t="n" s="0">
+        <v>1.10525E7</v>
+      </c>
+      <c r="E3" t="n" s="0">
+        <v>1.74362E7</v>
+      </c>
+      <c r="F3" t="n" s="0">
+        <v>1.11503E7</v>
+      </c>
+      <c r="G3" t="n" s="0">
+        <v>1.10572E7</v>
+      </c>
+      <c r="H3" t="n" s="0">
+        <v>1.10618E7</v>
+      </c>
+      <c r="I3" t="n" s="0">
+        <v>1.0512E7</v>
+      </c>
+      <c r="J3" t="n" s="0">
+        <v>1.06218E7</v>
+      </c>
+      <c r="K3" t="n" s="0">
+        <v>1.11538E7</v>
+      </c>
+      <c r="L3" t="n" s="0">
+        <v>1.7471E7</v>
+      </c>
+      <c r="M3" t="n" s="0">
+        <v>1.98551E7</v>
+      </c>
+      <c r="N3" t="n" s="0">
+        <v>1.75214E7</v>
+      </c>
+      <c r="O3" t="n" s="0">
+        <v>1.66768E7</v>
+      </c>
+      <c r="P3" t="n" s="0">
+        <v>1.84652E7</v>
+      </c>
+      <c r="Q3" t="n" s="0">
+        <v>2.28901E7</v>
+      </c>
+      <c r="R3" t="n" s="0">
+        <v>1.79003E7</v>
+      </c>
+      <c r="S3" t="n" s="0">
+        <v>1.76692E7</v>
+      </c>
+      <c r="T3" t="n" s="0">
+        <v>1.65213E7</v>
+      </c>
+      <c r="U3" t="n" s="0">
+        <v>1.64E7</v>
+      </c>
+      <c r="V3" t="n" s="0">
+        <v>1.82351E7</v>
+      </c>
+      <c r="W3" t="n" s="0">
+        <v>1.66344E7</v>
+      </c>
+      <c r="X3" t="n" s="0">
+        <v>1.71894E7</v>
+      </c>
+      <c r="Y3" t="n" s="0">
+        <v>1.77196E7</v>
+      </c>
+      <c r="Z3" t="n" s="0">
+        <v>1.77754E7</v>
+      </c>
+      <c r="AA3" t="n" s="0">
+        <v>1.82604E7</v>
+      </c>
+      <c r="AB3" t="n" s="0">
+        <v>1.77432E7</v>
+      </c>
+      <c r="AC3" t="n" s="0">
+        <v>1.74225E7</v>
+      </c>
+      <c r="AD3" t="n" s="0">
+        <v>1.66965E7</v>
+      </c>
+      <c r="AE3" t="n" s="0">
+        <v>1.6904E7</v>
+      </c>
+      <c r="AF3" t="n" s="0">
+        <v>1.96038E7</v>
+      </c>
+      <c r="AG3" t="n" s="0">
+        <v>1.76618E7</v>
+      </c>
+      <c r="AH3" t="n" s="0">
+        <v>1.67589E7</v>
+      </c>
+      <c r="AI3" t="n" s="0">
+        <v>1.70554E7</v>
+      </c>
+      <c r="AJ3" t="n" s="0">
+        <v>1.68725E7</v>
+      </c>
+      <c r="AK3" t="n" s="0">
+        <v>1.68144E7</v>
+      </c>
+      <c r="AL3" t="n" s="0">
+        <v>1.63793E7</v>
+      </c>
+      <c r="AM3" t="n" s="0">
+        <v>1.81743E7</v>
+      </c>
+      <c r="AN3" t="n" s="0">
+        <v>1.66183E7</v>
+      </c>
+      <c r="AO3" t="n" s="0">
+        <v>1.69109E7</v>
+      </c>
+      <c r="AP3" t="n" s="0">
+        <v>1.84605E7</v>
+      </c>
+      <c r="AQ3" t="n" s="0">
+        <v>2.04111E7</v>
+      </c>
+      <c r="AR3" t="n" s="0">
+        <v>1.81066E7</v>
+      </c>
+      <c r="AS3" t="n" s="0">
+        <v>1.75569E7</v>
+      </c>
+      <c r="AT3" t="n" s="0">
+        <v>1.64102E7</v>
+      </c>
+      <c r="AU3" t="n" s="0">
+        <v>1.70507E7</v>
+      </c>
+      <c r="AV3" t="n" s="0">
+        <v>1.69722E7</v>
+      </c>
+      <c r="AW3" t="n" s="0">
+        <v>1.79969E7</v>
+      </c>
+      <c r="AX3" t="n" s="0">
+        <v>1.68018E7</v>
+      </c>
+      <c r="AY3" t="n" s="0">
+        <v>1.6631E7</v>
+      </c>
+      <c r="AZ3" t="n" s="0">
+        <v>1.69022E7</v>
+      </c>
+      <c r="BA3" t="n" s="0">
+        <v>1.68379E7</v>
+      </c>
+      <c r="BB3" t="n" s="0">
+        <v>1.70764E7</v>
+      </c>
+      <c r="BC3" t="n" s="0">
+        <v>1.65271E7</v>
+      </c>
+      <c r="BD3" t="n" s="0">
+        <v>1.69129E7</v>
+      </c>
+      <c r="BE3" t="n" s="0">
+        <v>1.69706E7</v>
+      </c>
+      <c r="BF3" t="n" s="0">
+        <v>1.71647E7</v>
+      </c>
+      <c r="BG3" t="n" s="0">
+        <v>1.67823E7</v>
+      </c>
+      <c r="BH3" t="n" s="0">
+        <v>1.67232E7</v>
+      </c>
+      <c r="BI3" t="n" s="0">
+        <v>1.68969E7</v>
+      </c>
+      <c r="BJ3" t="n" s="0">
+        <v>1.66186E7</v>
+      </c>
+      <c r="BK3" t="n" s="0">
+        <v>1.68427E7</v>
+      </c>
+      <c r="BL3" t="n" s="0">
+        <v>1.73074E7</v>
+      </c>
+      <c r="BM3" t="n" s="0">
+        <v>1.68317E7</v>
+      </c>
+      <c r="BN3" t="n" s="0">
+        <v>1.69466E7</v>
+      </c>
+      <c r="BO3" t="n" s="0">
+        <v>1.90409E7</v>
+      </c>
+      <c r="BP3" t="n" s="0">
+        <v>1.68053E7</v>
+      </c>
+      <c r="BQ3" t="n" s="0">
+        <v>1.63909E7</v>
+      </c>
+      <c r="BR3" t="n" s="0">
+        <v>1.70317E7</v>
+      </c>
+      <c r="BS3" t="n" s="0">
+        <v>1.66439E7</v>
+      </c>
+      <c r="BT3" t="n" s="0">
+        <v>1.66218E7</v>
+      </c>
+      <c r="BU3" t="n" s="0">
+        <v>1.71684E7</v>
+      </c>
+      <c r="BV3" t="n" s="0">
+        <v>1.69777E7</v>
+      </c>
+      <c r="BW3" t="n" s="0">
+        <v>1.67354E7</v>
+      </c>
+      <c r="BX3" t="n" s="0">
+        <v>1.66704E7</v>
+      </c>
+      <c r="BY3" t="n" s="0">
+        <v>1.72881E7</v>
+      </c>
+      <c r="BZ3" t="n" s="0">
+        <v>1.94422E7</v>
+      </c>
+      <c r="CA3" t="n" s="0">
+        <v>1.86678E7</v>
+      </c>
+      <c r="CB3" t="n" s="0">
+        <v>1.81566E7</v>
+      </c>
+      <c r="CC3" t="n" s="0">
+        <v>1.77274E7</v>
+      </c>
+      <c r="CD3" t="n" s="0">
+        <v>1.74017E7</v>
+      </c>
+      <c r="CE3" t="n" s="0">
+        <v>1.75261E7</v>
+      </c>
+      <c r="CF3" t="n" s="0">
+        <v>1.68682E7</v>
+      </c>
+      <c r="CG3" t="n" s="0">
+        <v>1.68638E7</v>
+      </c>
+      <c r="CH3" t="n" s="0">
+        <v>1.7077E7</v>
+      </c>
+      <c r="CI3" t="n" s="0">
+        <v>1.66919E7</v>
+      </c>
+      <c r="CJ3" t="n" s="0">
+        <v>1.70942E7</v>
+      </c>
+      <c r="CK3" t="n" s="0">
+        <v>1.78015E7</v>
+      </c>
+      <c r="CL3" t="n" s="0">
+        <v>1.70981E7</v>
+      </c>
+      <c r="CM3" t="n" s="0">
+        <v>1.75262E7</v>
+      </c>
+      <c r="CN3" t="n" s="0">
+        <v>1.67903E7</v>
+      </c>
+      <c r="CO3" t="n" s="0">
+        <v>1.68525E7</v>
+      </c>
+      <c r="CP3" t="n" s="0">
+        <v>1.83634E7</v>
+      </c>
+      <c r="CQ3" t="n" s="0">
+        <v>1.81697E7</v>
+      </c>
+      <c r="CR3" t="n" s="0">
+        <v>1.82364E7</v>
+      </c>
+      <c r="CS3" t="n" s="0">
+        <v>1.72718E7</v>
+      </c>
+      <c r="CT3" t="n" s="0">
+        <v>1.78172E7</v>
+      </c>
+      <c r="CU3" t="n" s="0">
+        <v>1.80262E7</v>
+      </c>
+      <c r="CV3" t="n" s="0">
+        <v>1.79564E7</v>
+      </c>
+      <c r="CW3" t="n" s="0">
+        <v>1.80006E7</v>
+      </c>
+      <c r="CX3" t="n" s="0">
+        <v>1.85084E7</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="B4" t="n" s="0">
+        <v>5000.0</v>
+      </c>
+      <c r="C4" t="n" s="0">
+        <v>5713600.0</v>
+      </c>
+      <c r="D4" t="n" s="0">
+        <v>4224900.0</v>
+      </c>
+      <c r="E4" t="n" s="0">
+        <v>3131400.0</v>
+      </c>
+      <c r="F4" t="n" s="0">
+        <v>914800.0</v>
+      </c>
+      <c r="G4" t="n" s="0">
+        <v>946800.0</v>
+      </c>
+      <c r="H4" t="n" s="0">
+        <v>872900.0</v>
+      </c>
+      <c r="I4" t="n" s="0">
+        <v>839000.0</v>
+      </c>
+      <c r="J4" t="n" s="0">
+        <v>879900.0</v>
+      </c>
+      <c r="K4" t="n" s="0">
+        <v>881000.0</v>
+      </c>
+      <c r="L4" t="n" s="0">
+        <v>865300.0</v>
+      </c>
+      <c r="M4" t="n" s="0">
+        <v>908000.0</v>
+      </c>
+      <c r="N4" t="n" s="0">
+        <v>889900.0</v>
+      </c>
+      <c r="O4" t="n" s="0">
+        <v>866000.0</v>
+      </c>
+      <c r="P4" t="n" s="0">
+        <v>963600.0</v>
+      </c>
+      <c r="Q4" t="n" s="0">
+        <v>2144600.0</v>
+      </c>
+      <c r="R4" t="n" s="0">
+        <v>929900.0</v>
+      </c>
+      <c r="S4" t="n" s="0">
+        <v>936300.0</v>
+      </c>
+      <c r="T4" t="n" s="0">
+        <v>861200.0</v>
+      </c>
+      <c r="U4" t="n" s="0">
+        <v>894500.0</v>
+      </c>
+      <c r="V4" t="n" s="0">
+        <v>887500.0</v>
+      </c>
+      <c r="W4" t="n" s="0">
+        <v>847800.0</v>
+      </c>
+      <c r="X4" t="n" s="0">
+        <v>892800.0</v>
+      </c>
+      <c r="Y4" t="n" s="0">
+        <v>857000.0</v>
+      </c>
+      <c r="Z4" t="n" s="0">
+        <v>865600.0</v>
+      </c>
+      <c r="AA4" t="n" s="0">
+        <v>909300.0</v>
+      </c>
+      <c r="AB4" t="n" s="0">
+        <v>903200.0</v>
+      </c>
+      <c r="AC4" t="n" s="0">
+        <v>929400.0</v>
+      </c>
+      <c r="AD4" t="n" s="0">
+        <v>871400.0</v>
+      </c>
+      <c r="AE4" t="n" s="0">
+        <v>869700.0</v>
+      </c>
+      <c r="AF4" t="n" s="0">
+        <v>949700.0</v>
+      </c>
+      <c r="AG4" t="n" s="0">
+        <v>906600.0</v>
+      </c>
+      <c r="AH4" t="n" s="0">
+        <v>873600.0</v>
+      </c>
+      <c r="AI4" t="n" s="0">
+        <v>865900.0</v>
+      </c>
+      <c r="AJ4" t="n" s="0">
+        <v>857300.0</v>
+      </c>
+      <c r="AK4" t="n" s="0">
+        <v>870300.0</v>
+      </c>
+      <c r="AL4" t="n" s="0">
+        <v>850700.0</v>
+      </c>
+      <c r="AM4" t="n" s="0">
+        <v>855400.0</v>
+      </c>
+      <c r="AN4" t="n" s="0">
+        <v>857500.0</v>
+      </c>
+      <c r="AO4" t="n" s="0">
+        <v>866600.0</v>
+      </c>
+      <c r="AP4" t="n" s="0">
+        <v>940800.0</v>
+      </c>
+      <c r="AQ4" t="n" s="0">
+        <v>965500.0</v>
+      </c>
+      <c r="AR4" t="n" s="0">
+        <v>937000.0</v>
+      </c>
+      <c r="AS4" t="n" s="0">
+        <v>911000.0</v>
+      </c>
+      <c r="AT4" t="n" s="0">
+        <v>892600.0</v>
+      </c>
+      <c r="AU4" t="n" s="0">
+        <v>854500.0</v>
+      </c>
+      <c r="AV4" t="n" s="0">
+        <v>863300.0</v>
+      </c>
+      <c r="AW4" t="n" s="0">
+        <v>910900.0</v>
+      </c>
+      <c r="AX4" t="n" s="0">
+        <v>869500.0</v>
+      </c>
+      <c r="AY4" t="n" s="0">
+        <v>850700.0</v>
+      </c>
+      <c r="AZ4" t="n" s="0">
+        <v>876400.0</v>
+      </c>
+      <c r="BA4" t="n" s="0">
+        <v>864700.0</v>
+      </c>
+      <c r="BB4" t="n" s="0">
+        <v>893800.0</v>
+      </c>
+      <c r="BC4" t="n" s="0">
+        <v>890200.0</v>
+      </c>
+      <c r="BD4" t="n" s="0">
+        <v>870900.0</v>
+      </c>
+      <c r="BE4" t="n" s="0">
+        <v>877900.0</v>
+      </c>
+      <c r="BF4" t="n" s="0">
+        <v>861900.0</v>
+      </c>
+      <c r="BG4" t="n" s="0">
+        <v>1060900.0</v>
+      </c>
+      <c r="BH4" t="n" s="0">
+        <v>868400.0</v>
+      </c>
+      <c r="BI4" t="n" s="0">
+        <v>864700.0</v>
+      </c>
+      <c r="BJ4" t="n" s="0">
+        <v>868800.0</v>
+      </c>
+      <c r="BK4" t="n" s="0">
+        <v>855700.0</v>
+      </c>
+      <c r="BL4" t="n" s="0">
+        <v>845900.0</v>
+      </c>
+      <c r="BM4" t="n" s="0">
+        <v>888400.0</v>
+      </c>
+      <c r="BN4" t="n" s="0">
+        <v>870800.0</v>
+      </c>
+      <c r="BO4" t="n" s="0">
+        <v>1094200.0</v>
+      </c>
+      <c r="BP4" t="n" s="0">
+        <v>868300.0</v>
+      </c>
+      <c r="BQ4" t="n" s="0">
+        <v>963300.0</v>
+      </c>
+      <c r="BR4" t="n" s="0">
+        <v>870100.0</v>
+      </c>
+      <c r="BS4" t="n" s="0">
+        <v>833400.0</v>
+      </c>
+      <c r="BT4" t="n" s="0">
+        <v>834300.0</v>
+      </c>
+      <c r="BU4" t="n" s="0">
+        <v>844600.0</v>
+      </c>
+      <c r="BV4" t="n" s="0">
+        <v>851300.0</v>
+      </c>
+      <c r="BW4" t="n" s="0">
+        <v>888500.0</v>
+      </c>
+      <c r="BX4" t="n" s="0">
+        <v>863900.0</v>
+      </c>
+      <c r="BY4" t="n" s="0">
+        <v>901300.0</v>
+      </c>
+      <c r="BZ4" t="n" s="0">
+        <v>994600.0</v>
+      </c>
+      <c r="CA4" t="n" s="0">
+        <v>1023100.0</v>
+      </c>
+      <c r="CB4" t="n" s="0">
+        <v>959700.0</v>
+      </c>
+      <c r="CC4" t="n" s="0">
+        <v>903200.0</v>
+      </c>
+      <c r="CD4" t="n" s="0">
+        <v>859000.0</v>
+      </c>
+      <c r="CE4" t="n" s="0">
+        <v>901500.0</v>
+      </c>
+      <c r="CF4" t="n" s="0">
+        <v>910500.0</v>
+      </c>
+      <c r="CG4" t="n" s="0">
+        <v>851800.0</v>
+      </c>
+      <c r="CH4" t="n" s="0">
+        <v>880600.0</v>
+      </c>
+      <c r="CI4" t="n" s="0">
+        <v>912800.0</v>
+      </c>
+      <c r="CJ4" t="n" s="0">
+        <v>858300.0</v>
+      </c>
+      <c r="CK4" t="n" s="0">
+        <v>933800.0</v>
+      </c>
+      <c r="CL4" t="n" s="0">
+        <v>877200.0</v>
+      </c>
+      <c r="CM4" t="n" s="0">
+        <v>918100.0</v>
+      </c>
+      <c r="CN4" t="n" s="0">
+        <v>879900.0</v>
+      </c>
+      <c r="CO4" t="n" s="0">
+        <v>876800.0</v>
+      </c>
+      <c r="CP4" t="n" s="0">
+        <v>945600.0</v>
+      </c>
+      <c r="CQ4" t="n" s="0">
+        <v>974500.0</v>
+      </c>
+      <c r="CR4" t="n" s="0">
+        <v>935900.0</v>
+      </c>
+      <c r="CS4" t="n" s="0">
+        <v>935300.0</v>
+      </c>
+      <c r="CT4" t="n" s="0">
+        <v>947100.0</v>
+      </c>
+      <c r="CU4" t="n" s="0">
+        <v>933000.0</v>
+      </c>
+      <c r="CV4" t="n" s="0">
+        <v>969200.0</v>
+      </c>
+      <c r="CW4" t="n" s="0">
+        <v>944200.0</v>
+      </c>
+      <c r="CX4" t="n" s="0">
+        <v>937400.0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="B5" t="n" s="0">
+        <v>5000.0</v>
+      </c>
+      <c r="C5" t="n" s="0">
+        <v>7145900.0</v>
+      </c>
+      <c r="D5" t="n" s="0">
+        <v>5029000.0</v>
+      </c>
+      <c r="E5" t="n" s="0">
+        <v>3678700.0</v>
+      </c>
+      <c r="F5" t="n" s="0">
+        <v>913400.0</v>
+      </c>
+      <c r="G5" t="n" s="0">
+        <v>912000.0</v>
+      </c>
+      <c r="H5" t="n" s="0">
+        <v>835300.0</v>
+      </c>
+      <c r="I5" t="n" s="0">
+        <v>844200.0</v>
+      </c>
+      <c r="J5" t="n" s="0">
+        <v>828600.0</v>
+      </c>
+      <c r="K5" t="n" s="0">
+        <v>846700.0</v>
+      </c>
+      <c r="L5" t="n" s="0">
+        <v>841200.0</v>
+      </c>
+      <c r="M5" t="n" s="0">
+        <v>895400.0</v>
+      </c>
+      <c r="N5" t="n" s="0">
+        <v>899500.0</v>
+      </c>
+      <c r="O5" t="n" s="0">
+        <v>831300.0</v>
+      </c>
+      <c r="P5" t="n" s="0">
+        <v>1009200.0</v>
+      </c>
+      <c r="Q5" t="n" s="0">
+        <v>1149200.0</v>
+      </c>
+      <c r="R5" t="n" s="0">
+        <v>899800.0</v>
+      </c>
+      <c r="S5" t="n" s="0">
+        <v>894100.0</v>
+      </c>
+      <c r="T5" t="n" s="0">
+        <v>838200.0</v>
+      </c>
+      <c r="U5" t="n" s="0">
+        <v>830300.0</v>
+      </c>
+      <c r="V5" t="n" s="0">
+        <v>836500.0</v>
+      </c>
+      <c r="W5" t="n" s="0">
+        <v>833300.0</v>
+      </c>
+      <c r="X5" t="n" s="0">
+        <v>863100.0</v>
+      </c>
+      <c r="Y5" t="n" s="0">
+        <v>837700.0</v>
+      </c>
+      <c r="Z5" t="n" s="0">
+        <v>873800.0</v>
+      </c>
+      <c r="AA5" t="n" s="0">
+        <v>900000.0</v>
+      </c>
+      <c r="AB5" t="n" s="0">
+        <v>894900.0</v>
+      </c>
+      <c r="AC5" t="n" s="0">
+        <v>900200.0</v>
+      </c>
+      <c r="AD5" t="n" s="0">
+        <v>833600.0</v>
+      </c>
+      <c r="AE5" t="n" s="0">
+        <v>847000.0</v>
+      </c>
+      <c r="AF5" t="n" s="0">
+        <v>958300.0</v>
+      </c>
+      <c r="AG5" t="n" s="0">
+        <v>908000.0</v>
+      </c>
+      <c r="AH5" t="n" s="0">
+        <v>840900.0</v>
+      </c>
+      <c r="AI5" t="n" s="0">
+        <v>917500.0</v>
+      </c>
+      <c r="AJ5" t="n" s="0">
+        <v>856800.0</v>
+      </c>
+      <c r="AK5" t="n" s="0">
+        <v>851200.0</v>
+      </c>
+      <c r="AL5" t="n" s="0">
+        <v>906400.0</v>
+      </c>
+      <c r="AM5" t="n" s="0">
+        <v>843500.0</v>
+      </c>
+      <c r="AN5" t="n" s="0">
+        <v>835400.0</v>
+      </c>
+      <c r="AO5" t="n" s="0">
+        <v>860200.0</v>
+      </c>
+      <c r="AP5" t="n" s="0">
+        <v>899000.0</v>
+      </c>
+      <c r="AQ5" t="n" s="0">
+        <v>1030200.0</v>
+      </c>
+      <c r="AR5" t="n" s="0">
+        <v>894600.0</v>
+      </c>
+      <c r="AS5" t="n" s="0">
+        <v>889200.0</v>
+      </c>
+      <c r="AT5" t="n" s="0">
+        <v>831000.0</v>
+      </c>
+      <c r="AU5" t="n" s="0">
+        <v>851500.0</v>
+      </c>
+      <c r="AV5" t="n" s="0">
+        <v>845400.0</v>
+      </c>
+      <c r="AW5" t="n" s="0">
+        <v>849100.0</v>
+      </c>
+      <c r="AX5" t="n" s="0">
+        <v>848700.0</v>
+      </c>
+      <c r="AY5" t="n" s="0">
+        <v>840300.0</v>
+      </c>
+      <c r="AZ5" t="n" s="0">
+        <v>846100.0</v>
+      </c>
+      <c r="BA5" t="n" s="0">
+        <v>823300.0</v>
+      </c>
+      <c r="BB5" t="n" s="0">
+        <v>918300.0</v>
+      </c>
+      <c r="BC5" t="n" s="0">
+        <v>839700.0</v>
+      </c>
+      <c r="BD5" t="n" s="0">
+        <v>852200.0</v>
+      </c>
+      <c r="BE5" t="n" s="0">
+        <v>847700.0</v>
+      </c>
+      <c r="BF5" t="n" s="0">
+        <v>836300.0</v>
+      </c>
+      <c r="BG5" t="n" s="0">
+        <v>871500.0</v>
+      </c>
+      <c r="BH5" t="n" s="0">
+        <v>916500.0</v>
+      </c>
+      <c r="BI5" t="n" s="0">
+        <v>860200.0</v>
+      </c>
+      <c r="BJ5" t="n" s="0">
+        <v>835200.0</v>
+      </c>
+      <c r="BK5" t="n" s="0">
+        <v>854800.0</v>
+      </c>
+      <c r="BL5" t="n" s="0">
+        <v>845600.0</v>
+      </c>
+      <c r="BM5" t="n" s="0">
+        <v>856400.0</v>
+      </c>
+      <c r="BN5" t="n" s="0">
+        <v>851500.0</v>
+      </c>
+      <c r="BO5" t="n" s="0">
+        <v>896900.0</v>
+      </c>
+      <c r="BP5" t="n" s="0">
+        <v>853000.0</v>
+      </c>
+      <c r="BQ5" t="n" s="0">
+        <v>1002200.0</v>
+      </c>
+      <c r="BR5" t="n" s="0">
+        <v>859300.0</v>
+      </c>
+      <c r="BS5" t="n" s="0">
+        <v>836300.0</v>
+      </c>
+      <c r="BT5" t="n" s="0">
+        <v>845800.0</v>
+      </c>
+      <c r="BU5" t="n" s="0">
+        <v>853500.0</v>
+      </c>
+      <c r="BV5" t="n" s="0">
+        <v>1439400.0</v>
+      </c>
+      <c r="BW5" t="n" s="0">
+        <v>878300.0</v>
+      </c>
+      <c r="BX5" t="n" s="0">
+        <v>881000.0</v>
+      </c>
+      <c r="BY5" t="n" s="0">
+        <v>942300.0</v>
+      </c>
+      <c r="BZ5" t="n" s="0">
+        <v>962500.0</v>
+      </c>
+      <c r="CA5" t="n" s="0">
+        <v>976300.0</v>
+      </c>
+      <c r="CB5" t="n" s="0">
+        <v>926100.0</v>
+      </c>
+      <c r="CC5" t="n" s="0">
+        <v>910100.0</v>
+      </c>
+      <c r="CD5" t="n" s="0">
+        <v>860800.0</v>
+      </c>
+      <c r="CE5" t="n" s="0">
+        <v>855600.0</v>
+      </c>
+      <c r="CF5" t="n" s="0">
+        <v>841600.0</v>
+      </c>
+      <c r="CG5" t="n" s="0">
+        <v>849600.0</v>
+      </c>
+      <c r="CH5" t="n" s="0">
+        <v>911200.0</v>
+      </c>
+      <c r="CI5" t="n" s="0">
+        <v>893900.0</v>
+      </c>
+      <c r="CJ5" t="n" s="0">
+        <v>1044700.0</v>
+      </c>
+      <c r="CK5" t="n" s="0">
+        <v>891600.0</v>
+      </c>
+      <c r="CL5" t="n" s="0">
+        <v>863900.0</v>
+      </c>
+      <c r="CM5" t="n" s="0">
+        <v>908100.0</v>
+      </c>
+      <c r="CN5" t="n" s="0">
+        <v>845200.0</v>
+      </c>
+      <c r="CO5" t="n" s="0">
+        <v>829900.0</v>
+      </c>
+      <c r="CP5" t="n" s="0">
+        <v>891900.0</v>
+      </c>
+      <c r="CQ5" t="n" s="0">
+        <v>902000.0</v>
+      </c>
+      <c r="CR5" t="n" s="0">
+        <v>913600.0</v>
+      </c>
+      <c r="CS5" t="n" s="0">
+        <v>910600.0</v>
+      </c>
+      <c r="CT5" t="n" s="0">
+        <v>918100.0</v>
+      </c>
+      <c r="CU5" t="n" s="0">
+        <v>931800.0</v>
+      </c>
+      <c r="CV5" t="n" s="0">
+        <v>918800.0</v>
+      </c>
+      <c r="CW5" t="n" s="0">
+        <v>916000.0</v>
+      </c>
+      <c r="CX5" t="n" s="0">
+        <v>923400.0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="B6" t="n" s="0">
+        <v>5000.0</v>
+      </c>
+      <c r="C6" t="n" s="0">
+        <v>8169000.0</v>
+      </c>
+      <c r="D6" t="n" s="0">
+        <v>6695400.0</v>
+      </c>
+      <c r="E6" t="n" s="0">
+        <v>4487100.0</v>
+      </c>
+      <c r="F6" t="n" s="0">
+        <v>7038900.0</v>
+      </c>
+      <c r="G6" t="n" s="0">
+        <v>6642700.0</v>
+      </c>
+      <c r="H6" t="n" s="0">
+        <v>6304100.0</v>
+      </c>
+      <c r="I6" t="n" s="0">
+        <v>6153300.0</v>
+      </c>
+      <c r="J6" t="n" s="0">
+        <v>6282400.0</v>
+      </c>
+      <c r="K6" t="n" s="0">
+        <v>6602300.0</v>
+      </c>
+      <c r="L6" t="n" s="0">
+        <v>4125300.0</v>
+      </c>
+      <c r="M6" t="n" s="0">
+        <v>4452600.0</v>
+      </c>
+      <c r="N6" t="n" s="0">
+        <v>4410000.0</v>
+      </c>
+      <c r="O6" t="n" s="0">
+        <v>4409800.0</v>
+      </c>
+      <c r="P6" t="n" s="0">
+        <v>4474800.0</v>
+      </c>
+      <c r="Q6" t="n" s="0">
+        <v>5054400.0</v>
+      </c>
+      <c r="R6" t="n" s="0">
+        <v>4416300.0</v>
+      </c>
+      <c r="S6" t="n" s="0">
+        <v>4552700.0</v>
+      </c>
+      <c r="T6" t="n" s="0">
+        <v>4558200.0</v>
+      </c>
+      <c r="U6" t="n" s="0">
+        <v>4314400.0</v>
+      </c>
+      <c r="V6" t="n" s="0">
+        <v>4309800.0</v>
+      </c>
+      <c r="W6" t="n" s="0">
+        <v>4135900.0</v>
+      </c>
+      <c r="X6" t="n" s="0">
+        <v>4498300.0</v>
+      </c>
+      <c r="Y6" t="n" s="0">
+        <v>4206700.0</v>
+      </c>
+      <c r="Z6" t="n" s="0">
+        <v>4472700.0</v>
+      </c>
+      <c r="AA6" t="n" s="0">
+        <v>4416200.0</v>
+      </c>
+      <c r="AB6" t="n" s="0">
+        <v>4452900.0</v>
+      </c>
+      <c r="AC6" t="n" s="0">
+        <v>4496000.0</v>
+      </c>
+      <c r="AD6" t="n" s="0">
+        <v>4359300.0</v>
+      </c>
+      <c r="AE6" t="n" s="0">
+        <v>4134500.0</v>
+      </c>
+      <c r="AF6" t="n" s="0">
+        <v>4664700.0</v>
+      </c>
+      <c r="AG6" t="n" s="0">
+        <v>4916000.0</v>
+      </c>
+      <c r="AH6" t="n" s="0">
+        <v>4191300.0</v>
+      </c>
+      <c r="AI6" t="n" s="0">
+        <v>4244600.0</v>
+      </c>
+      <c r="AJ6" t="n" s="0">
+        <v>4469500.0</v>
+      </c>
+      <c r="AK6" t="n" s="0">
+        <v>4129000.0</v>
+      </c>
+      <c r="AL6" t="n" s="0">
+        <v>4177800.0</v>
+      </c>
+      <c r="AM6" t="n" s="0">
+        <v>4149700.0</v>
+      </c>
+      <c r="AN6" t="n" s="0">
+        <v>4139700.0</v>
+      </c>
+      <c r="AO6" t="n" s="0">
+        <v>4472600.0</v>
+      </c>
+      <c r="AP6" t="n" s="0">
+        <v>4456800.0</v>
+      </c>
+      <c r="AQ6" t="n" s="0">
+        <v>4630600.0</v>
+      </c>
+      <c r="AR6" t="n" s="0">
+        <v>4254700.0</v>
+      </c>
+      <c r="AS6" t="n" s="0">
+        <v>4464300.0</v>
+      </c>
+      <c r="AT6" t="n" s="0">
+        <v>4508900.0</v>
+      </c>
+      <c r="AU6" t="n" s="0">
+        <v>4488900.0</v>
+      </c>
+      <c r="AV6" t="n" s="0">
+        <v>4212200.0</v>
+      </c>
+      <c r="AW6" t="n" s="0">
+        <v>4185300.0</v>
+      </c>
+      <c r="AX6" t="n" s="0">
+        <v>4429900.0</v>
+      </c>
+      <c r="AY6" t="n" s="0">
+        <v>4775700.0</v>
+      </c>
+      <c r="AZ6" t="n" s="0">
+        <v>4117100.0</v>
+      </c>
+      <c r="BA6" t="n" s="0">
+        <v>4224600.0</v>
+      </c>
+      <c r="BB6" t="n" s="0">
+        <v>4395700.0</v>
+      </c>
+      <c r="BC6" t="n" s="0">
+        <v>4151500.0</v>
+      </c>
+      <c r="BD6" t="n" s="0">
+        <v>4146800.0</v>
+      </c>
+      <c r="BE6" t="n" s="0">
+        <v>4233400.0</v>
+      </c>
+      <c r="BF6" t="n" s="0">
+        <v>4545400.0</v>
+      </c>
+      <c r="BG6" t="n" s="0">
+        <v>4306000.0</v>
+      </c>
+      <c r="BH6" t="n" s="0">
+        <v>4120600.0</v>
+      </c>
+      <c r="BI6" t="n" s="0">
+        <v>4199300.0</v>
+      </c>
+      <c r="BJ6" t="n" s="0">
+        <v>4192300.0</v>
+      </c>
+      <c r="BK6" t="n" s="0">
+        <v>4250900.0</v>
+      </c>
+      <c r="BL6" t="n" s="0">
+        <v>4697300.0</v>
+      </c>
+      <c r="BM6" t="n" s="0">
+        <v>4200000.0</v>
+      </c>
+      <c r="BN6" t="n" s="0">
+        <v>4131100.0</v>
+      </c>
+      <c r="BO6" t="n" s="0">
+        <v>4224200.0</v>
+      </c>
+      <c r="BP6" t="n" s="0">
+        <v>4418400.0</v>
+      </c>
+      <c r="BQ6" t="n" s="0">
+        <v>4433700.0</v>
+      </c>
+      <c r="BR6" t="n" s="0">
+        <v>4280300.0</v>
+      </c>
+      <c r="BS6" t="n" s="0">
+        <v>4147900.0</v>
+      </c>
+      <c r="BT6" t="n" s="0">
+        <v>4411600.0</v>
+      </c>
+      <c r="BU6" t="n" s="0">
+        <v>4280700.0</v>
+      </c>
+      <c r="BV6" t="n" s="0">
+        <v>4176500.0</v>
+      </c>
+      <c r="BW6" t="n" s="0">
+        <v>4138100.0</v>
+      </c>
+      <c r="BX6" t="n" s="0">
+        <v>4427700.0</v>
+      </c>
+      <c r="BY6" t="n" s="0">
+        <v>4439600.0</v>
+      </c>
+      <c r="BZ6" t="n" s="0">
+        <v>4746000.0</v>
+      </c>
+      <c r="CA6" t="n" s="0">
+        <v>4641200.0</v>
+      </c>
+      <c r="CB6" t="n" s="0">
+        <v>4882100.0</v>
+      </c>
+      <c r="CC6" t="n" s="0">
+        <v>4408900.0</v>
+      </c>
+      <c r="CD6" t="n" s="0">
+        <v>4151000.0</v>
+      </c>
+      <c r="CE6" t="n" s="0">
+        <v>4153100.0</v>
+      </c>
+      <c r="CF6" t="n" s="0">
+        <v>4117400.0</v>
+      </c>
+      <c r="CG6" t="n" s="0">
+        <v>4694400.0</v>
+      </c>
+      <c r="CH6" t="n" s="0">
+        <v>4147100.0</v>
+      </c>
+      <c r="CI6" t="n" s="0">
+        <v>4414100.0</v>
+      </c>
+      <c r="CJ6" t="n" s="0">
+        <v>4126000.0</v>
+      </c>
+      <c r="CK6" t="n" s="0">
+        <v>4459800.0</v>
+      </c>
+      <c r="CL6" t="n" s="0">
+        <v>4186200.0</v>
+      </c>
+      <c r="CM6" t="n" s="0">
+        <v>4390400.0</v>
+      </c>
+      <c r="CN6" t="n" s="0">
+        <v>4388500.0</v>
+      </c>
+      <c r="CO6" t="n" s="0">
+        <v>4138800.0</v>
+      </c>
+      <c r="CP6" t="n" s="0">
+        <v>4507000.0</v>
+      </c>
+      <c r="CQ6" t="n" s="0">
+        <v>4515200.0</v>
+      </c>
+      <c r="CR6" t="n" s="0">
+        <v>4475500.0</v>
+      </c>
+      <c r="CS6" t="n" s="0">
+        <v>4435700.0</v>
+      </c>
+      <c r="CT6" t="n" s="0">
+        <v>4515800.0</v>
+      </c>
+      <c r="CU6" t="n" s="0">
+        <v>4487800.0</v>
+      </c>
+      <c r="CV6" t="n" s="0">
+        <v>4451500.0</v>
+      </c>
+      <c r="CW6" t="n" s="0">
+        <v>4470900.0</v>
+      </c>
+      <c r="CX6" t="n" s="0">
+        <v>4462700.0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="B7" t="n" s="0">
+        <v>5000.0</v>
+      </c>
+      <c r="C7" t="n" s="0">
+        <v>8243500.0</v>
+      </c>
+      <c r="D7" t="n" s="0">
+        <v>6628100.0</v>
+      </c>
+      <c r="E7" t="n" s="0">
+        <v>4542100.0</v>
+      </c>
+      <c r="F7" t="n" s="0">
+        <v>6681800.0</v>
+      </c>
+      <c r="G7" t="n" s="0">
+        <v>6593800.0</v>
+      </c>
+      <c r="H7" t="n" s="0">
+        <v>6172500.0</v>
+      </c>
+      <c r="I7" t="n" s="0">
+        <v>6336900.0</v>
+      </c>
+      <c r="J7" t="n" s="0">
+        <v>6166200.0</v>
+      </c>
+      <c r="K7" t="n" s="0">
+        <v>6253800.0</v>
+      </c>
+      <c r="L7" t="n" s="0">
+        <v>4190500.0</v>
+      </c>
+      <c r="M7" t="n" s="0">
+        <v>4466500.0</v>
+      </c>
+      <c r="N7" t="n" s="0">
+        <v>4283500.0</v>
+      </c>
+      <c r="O7" t="n" s="0">
+        <v>4144400.0</v>
+      </c>
+      <c r="P7" t="n" s="0">
+        <v>4848400.0</v>
+      </c>
+      <c r="Q7" t="n" s="0">
+        <v>6738300.0</v>
+      </c>
+      <c r="R7" t="n" s="0">
+        <v>4418200.0</v>
+      </c>
+      <c r="S7" t="n" s="0">
+        <v>4212600.0</v>
+      </c>
+      <c r="T7" t="n" s="0">
+        <v>4242800.0</v>
+      </c>
+      <c r="U7" t="n" s="0">
+        <v>4219600.0</v>
+      </c>
+      <c r="V7" t="n" s="0">
+        <v>4161500.0</v>
+      </c>
+      <c r="W7" t="n" s="0">
+        <v>4119300.0</v>
+      </c>
+      <c r="X7" t="n" s="0">
+        <v>4426900.0</v>
+      </c>
+      <c r="Y7" t="n" s="0">
+        <v>4183600.0</v>
+      </c>
+      <c r="Z7" t="n" s="0">
+        <v>4495500.0</v>
+      </c>
+      <c r="AA7" t="n" s="0">
+        <v>4561000.0</v>
+      </c>
+      <c r="AB7" t="n" s="0">
+        <v>4179000.0</v>
+      </c>
+      <c r="AC7" t="n" s="0">
+        <v>4274300.0</v>
+      </c>
+      <c r="AD7" t="n" s="0">
+        <v>4191800.0</v>
+      </c>
+      <c r="AE7" t="n" s="0">
+        <v>4157600.0</v>
+      </c>
+      <c r="AF7" t="n" s="0">
+        <v>4707200.0</v>
+      </c>
+      <c r="AG7" t="n" s="0">
+        <v>5106500.0</v>
+      </c>
+      <c r="AH7" t="n" s="0">
+        <v>4139500.0</v>
+      </c>
+      <c r="AI7" t="n" s="0">
+        <v>4165800.0</v>
+      </c>
+      <c r="AJ7" t="n" s="0">
+        <v>4465300.0</v>
+      </c>
+      <c r="AK7" t="n" s="0">
+        <v>4420200.0</v>
+      </c>
+      <c r="AL7" t="n" s="0">
+        <v>4377000.0</v>
+      </c>
+      <c r="AM7" t="n" s="0">
+        <v>4167900.0</v>
+      </c>
+      <c r="AN7" t="n" s="0">
+        <v>4149300.0</v>
+      </c>
+      <c r="AO7" t="n" s="0">
+        <v>4474900.0</v>
+      </c>
+      <c r="AP7" t="n" s="0">
+        <v>4500000.0</v>
+      </c>
+      <c r="AQ7" t="n" s="0">
+        <v>4648000.0</v>
+      </c>
+      <c r="AR7" t="n" s="0">
+        <v>4360300.0</v>
+      </c>
+      <c r="AS7" t="n" s="0">
+        <v>4417800.0</v>
+      </c>
+      <c r="AT7" t="n" s="0">
+        <v>4167000.0</v>
+      </c>
+      <c r="AU7" t="n" s="0">
+        <v>4155500.0</v>
+      </c>
+      <c r="AV7" t="n" s="0">
+        <v>4131200.0</v>
+      </c>
+      <c r="AW7" t="n" s="0">
+        <v>4175800.0</v>
+      </c>
+      <c r="AX7" t="n" s="0">
+        <v>4833200.0</v>
+      </c>
+      <c r="AY7" t="n" s="0">
+        <v>4154000.0</v>
+      </c>
+      <c r="AZ7" t="n" s="0">
+        <v>4340200.0</v>
+      </c>
+      <c r="BA7" t="n" s="0">
+        <v>4732600.0</v>
+      </c>
+      <c r="BB7" t="n" s="0">
+        <v>4206400.0</v>
+      </c>
+      <c r="BC7" t="n" s="0">
+        <v>4137100.0</v>
+      </c>
+      <c r="BD7" t="n" s="0">
+        <v>4148600.0</v>
+      </c>
+      <c r="BE7" t="n" s="0">
+        <v>4150800.0</v>
+      </c>
+      <c r="BF7" t="n" s="0">
+        <v>4130200.0</v>
+      </c>
+      <c r="BG7" t="n" s="0">
+        <v>4185200.0</v>
+      </c>
+      <c r="BH7" t="n" s="0">
+        <v>4183000.0</v>
+      </c>
+      <c r="BI7" t="n" s="0">
+        <v>4179000.0</v>
+      </c>
+      <c r="BJ7" t="n" s="0">
+        <v>4473100.0</v>
+      </c>
+      <c r="BK7" t="n" s="0">
+        <v>4145700.0</v>
+      </c>
+      <c r="BL7" t="n" s="0">
+        <v>4140400.0</v>
+      </c>
+      <c r="BM7" t="n" s="0">
+        <v>4176400.0</v>
+      </c>
+      <c r="BN7" t="n" s="0">
+        <v>4198600.0</v>
+      </c>
+      <c r="BO7" t="n" s="0">
+        <v>4466100.0</v>
+      </c>
+      <c r="BP7" t="n" s="0">
+        <v>6190100.0</v>
+      </c>
+      <c r="BQ7" t="n" s="0">
+        <v>4507400.0</v>
+      </c>
+      <c r="BR7" t="n" s="0">
+        <v>4133000.0</v>
+      </c>
+      <c r="BS7" t="n" s="0">
+        <v>4217200.0</v>
+      </c>
+      <c r="BT7" t="n" s="0">
+        <v>4249200.0</v>
+      </c>
+      <c r="BU7" t="n" s="0">
+        <v>4209400.0</v>
+      </c>
+      <c r="BV7" t="n" s="0">
+        <v>4158500.0</v>
+      </c>
+      <c r="BW7" t="n" s="0">
+        <v>4201000.0</v>
+      </c>
+      <c r="BX7" t="n" s="0">
+        <v>4420300.0</v>
+      </c>
+      <c r="BY7" t="n" s="0">
+        <v>4717500.0</v>
+      </c>
+      <c r="BZ7" t="n" s="0">
+        <v>4622700.0</v>
+      </c>
+      <c r="CA7" t="n" s="0">
+        <v>4641800.0</v>
+      </c>
+      <c r="CB7" t="n" s="0">
+        <v>4772200.0</v>
+      </c>
+      <c r="CC7" t="n" s="0">
+        <v>4410700.0</v>
+      </c>
+      <c r="CD7" t="n" s="0">
+        <v>4346000.0</v>
+      </c>
+      <c r="CE7" t="n" s="0">
+        <v>4288900.0</v>
+      </c>
+      <c r="CF7" t="n" s="0">
+        <v>4377400.0</v>
+      </c>
+      <c r="CG7" t="n" s="0">
+        <v>4254400.0</v>
+      </c>
+      <c r="CH7" t="n" s="0">
+        <v>4152500.0</v>
+      </c>
+      <c r="CI7" t="n" s="0">
+        <v>4737500.0</v>
+      </c>
+      <c r="CJ7" t="n" s="0">
+        <v>4360600.0</v>
+      </c>
+      <c r="CK7" t="n" s="0">
+        <v>4436800.0</v>
+      </c>
+      <c r="CL7" t="n" s="0">
+        <v>4251400.0</v>
+      </c>
+      <c r="CM7" t="n" s="0">
+        <v>4178300.0</v>
+      </c>
+      <c r="CN7" t="n" s="0">
+        <v>4145700.0</v>
+      </c>
+      <c r="CO7" t="n" s="0">
+        <v>4178300.0</v>
+      </c>
+      <c r="CP7" t="n" s="0">
+        <v>4521600.0</v>
+      </c>
+      <c r="CQ7" t="n" s="0">
+        <v>4475600.0</v>
+      </c>
+      <c r="CR7" t="n" s="0">
+        <v>4482500.0</v>
+      </c>
+      <c r="CS7" t="n" s="0">
+        <v>4483500.0</v>
+      </c>
+      <c r="CT7" t="n" s="0">
+        <v>4536200.0</v>
+      </c>
+      <c r="CU7" t="n" s="0">
+        <v>4503800.0</v>
+      </c>
+      <c r="CV7" t="n" s="0">
+        <v>4506900.0</v>
+      </c>
+      <c r="CW7" t="n" s="0">
+        <v>4480500.0</v>
+      </c>
+      <c r="CX7" t="n" s="0">
+        <v>4474900.0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="B8" t="n" s="0">
+        <v>5000.0</v>
+      </c>
+      <c r="C8" t="n" s="0">
+        <v>1055800.0</v>
+      </c>
+      <c r="D8" t="n" s="0">
+        <v>450500.0</v>
+      </c>
+      <c r="E8" t="n" s="0">
+        <v>502100.0</v>
+      </c>
+      <c r="F8" t="n" s="0">
+        <v>401600.0</v>
+      </c>
+      <c r="G8" t="n" s="0">
+        <v>494500.0</v>
+      </c>
+      <c r="H8" t="n" s="0">
+        <v>422600.0</v>
+      </c>
+      <c r="I8" t="n" s="0">
+        <v>426500.0</v>
+      </c>
+      <c r="J8" t="n" s="0">
+        <v>444600.0</v>
+      </c>
+      <c r="K8" t="n" s="0">
+        <v>368800.0</v>
+      </c>
+      <c r="L8" t="n" s="0">
+        <v>360000.0</v>
+      </c>
+      <c r="M8" t="n" s="0">
+        <v>450900.0</v>
+      </c>
+      <c r="N8" t="n" s="0">
+        <v>392600.0</v>
+      </c>
+      <c r="O8" t="n" s="0">
+        <v>478000.0</v>
+      </c>
+      <c r="P8" t="n" s="0">
+        <v>420000.0</v>
+      </c>
+      <c r="Q8" t="n" s="0">
+        <v>496300.0</v>
+      </c>
+      <c r="R8" t="n" s="0">
+        <v>488300.0</v>
+      </c>
+      <c r="S8" t="n" s="0">
+        <v>582100.0</v>
+      </c>
+      <c r="T8" t="n" s="0">
+        <v>482800.0</v>
+      </c>
+      <c r="U8" t="n" s="0">
+        <v>484900.0</v>
+      </c>
+      <c r="V8" t="n" s="0">
+        <v>484300.0</v>
+      </c>
+      <c r="W8" t="n" s="0">
+        <v>352100.0</v>
+      </c>
+      <c r="X8" t="n" s="0">
+        <v>439400.0</v>
+      </c>
+      <c r="Y8" t="n" s="0">
+        <v>419600.0</v>
+      </c>
+      <c r="Z8" t="n" s="0">
+        <v>387600.0</v>
+      </c>
+      <c r="AA8" t="n" s="0">
+        <v>400600.0</v>
+      </c>
+      <c r="AB8" t="n" s="0">
+        <v>449800.0</v>
+      </c>
+      <c r="AC8" t="n" s="0">
+        <v>389600.0</v>
+      </c>
+      <c r="AD8" t="n" s="0">
+        <v>499900.0</v>
+      </c>
+      <c r="AE8" t="n" s="0">
+        <v>357300.0</v>
+      </c>
+      <c r="AF8" t="n" s="0">
+        <v>437900.0</v>
+      </c>
+      <c r="AG8" t="n" s="0">
+        <v>501000.0</v>
+      </c>
+      <c r="AH8" t="n" s="0">
+        <v>484600.0</v>
+      </c>
+      <c r="AI8" t="n" s="0">
+        <v>391000.0</v>
+      </c>
+      <c r="AJ8" t="n" s="0">
+        <v>397200.0</v>
+      </c>
+      <c r="AK8" t="n" s="0">
+        <v>446500.0</v>
+      </c>
+      <c r="AL8" t="n" s="0">
+        <v>404500.0</v>
+      </c>
+      <c r="AM8" t="n" s="0">
+        <v>444800.0</v>
+      </c>
+      <c r="AN8" t="n" s="0">
+        <v>384900.0</v>
+      </c>
+      <c r="AO8" t="n" s="0">
+        <v>386700.0</v>
+      </c>
+      <c r="AP8" t="n" s="0">
+        <v>497900.0</v>
+      </c>
+      <c r="AQ8" t="n" s="0">
+        <v>479400.0</v>
+      </c>
+      <c r="AR8" t="n" s="0">
+        <v>448700.0</v>
+      </c>
+      <c r="AS8" t="n" s="0">
+        <v>480400.0</v>
+      </c>
+      <c r="AT8" t="n" s="0">
+        <v>434200.0</v>
+      </c>
+      <c r="AU8" t="n" s="0">
+        <v>465200.0</v>
+      </c>
+      <c r="AV8" t="n" s="0">
+        <v>450200.0</v>
+      </c>
+      <c r="AW8" t="n" s="0">
+        <v>443600.0</v>
+      </c>
+      <c r="AX8" t="n" s="0">
+        <v>478400.0</v>
+      </c>
+      <c r="AY8" t="n" s="0">
+        <v>445000.0</v>
+      </c>
+      <c r="AZ8" t="n" s="0">
+        <v>464900.0</v>
+      </c>
+      <c r="BA8" t="n" s="0">
+        <v>479600.0</v>
+      </c>
+      <c r="BB8" t="n" s="0">
+        <v>434900.0</v>
+      </c>
+      <c r="BC8" t="n" s="0">
+        <v>364700.0</v>
+      </c>
+      <c r="BD8" t="n" s="0">
+        <v>396000.0</v>
+      </c>
+      <c r="BE8" t="n" s="0">
+        <v>400800.0</v>
+      </c>
+      <c r="BF8" t="n" s="0">
+        <v>437600.0</v>
+      </c>
+      <c r="BG8" t="n" s="0">
+        <v>396400.0</v>
+      </c>
+      <c r="BH8" t="n" s="0">
+        <v>392600.0</v>
+      </c>
+      <c r="BI8" t="n" s="0">
+        <v>396000.0</v>
+      </c>
+      <c r="BJ8" t="n" s="0">
+        <v>407700.0</v>
+      </c>
+      <c r="BK8" t="n" s="0">
+        <v>423600.0</v>
+      </c>
+      <c r="BL8" t="n" s="0">
+        <v>386900.0</v>
+      </c>
+      <c r="BM8" t="n" s="0">
+        <v>351200.0</v>
+      </c>
+      <c r="BN8" t="n" s="0">
+        <v>363000.0</v>
+      </c>
+      <c r="BO8" t="n" s="0">
+        <v>391900.0</v>
+      </c>
+      <c r="BP8" t="n" s="0">
+        <v>490700.0</v>
+      </c>
+      <c r="BQ8" t="n" s="0">
+        <v>387000.0</v>
+      </c>
+      <c r="BR8" t="n" s="0">
+        <v>433500.0</v>
+      </c>
+      <c r="BS8" t="n" s="0">
+        <v>363300.0</v>
+      </c>
+      <c r="BT8" t="n" s="0">
+        <v>373700.0</v>
+      </c>
+      <c r="BU8" t="n" s="0">
+        <v>384400.0</v>
+      </c>
+      <c r="BV8" t="n" s="0">
+        <v>390500.0</v>
+      </c>
+      <c r="BW8" t="n" s="0">
+        <v>384000.0</v>
+      </c>
+      <c r="BX8" t="n" s="0">
+        <v>699700.0</v>
+      </c>
+      <c r="BY8" t="n" s="0">
+        <v>414800.0</v>
+      </c>
+      <c r="BZ8" t="n" s="0">
+        <v>406200.0</v>
+      </c>
+      <c r="CA8" t="n" s="0">
+        <v>416000.0</v>
+      </c>
+      <c r="CB8" t="n" s="0">
+        <v>418000.0</v>
+      </c>
+      <c r="CC8" t="n" s="0">
+        <v>468400.0</v>
+      </c>
+      <c r="CD8" t="n" s="0">
+        <v>3.15636E7</v>
+      </c>
+      <c r="CE8" t="n" s="0">
+        <v>407900.0</v>
+      </c>
+      <c r="CF8" t="n" s="0">
+        <v>400700.0</v>
+      </c>
+      <c r="CG8" t="n" s="0">
+        <v>478400.0</v>
+      </c>
+      <c r="CH8" t="n" s="0">
+        <v>459600.0</v>
+      </c>
+      <c r="CI8" t="n" s="0">
+        <v>504700.0</v>
+      </c>
+      <c r="CJ8" t="n" s="0">
+        <v>448200.0</v>
+      </c>
+      <c r="CK8" t="n" s="0">
+        <v>473800.0</v>
+      </c>
+      <c r="CL8" t="n" s="0">
+        <v>475000.0</v>
+      </c>
+      <c r="CM8" t="n" s="0">
+        <v>422500.0</v>
+      </c>
+      <c r="CN8" t="n" s="0">
+        <v>451800.0</v>
+      </c>
+      <c r="CO8" t="n" s="0">
+        <v>451000.0</v>
+      </c>
+      <c r="CP8" t="n" s="0">
+        <v>487100.0</v>
+      </c>
+      <c r="CQ8" t="n" s="0">
+        <v>474200.0</v>
+      </c>
+      <c r="CR8" t="n" s="0">
+        <v>510600.0</v>
+      </c>
+      <c r="CS8" t="n" s="0">
+        <v>470000.0</v>
+      </c>
+      <c r="CT8" t="n" s="0">
+        <v>515100.0</v>
+      </c>
+      <c r="CU8" t="n" s="0">
+        <v>509100.0</v>
+      </c>
+      <c r="CV8" t="n" s="0">
+        <v>500500.0</v>
+      </c>
+      <c r="CW8" t="n" s="0">
+        <v>484400.0</v>
+      </c>
+      <c r="CX8" t="n" s="0">
+        <v>508600.0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="B9" t="n" s="0">
+        <v>5000.0</v>
+      </c>
+      <c r="C9" t="n" s="0">
+        <v>1483100.0</v>
+      </c>
+      <c r="D9" t="n" s="0">
+        <v>401900.0</v>
+      </c>
+      <c r="E9" t="n" s="0">
+        <v>554800.0</v>
+      </c>
+      <c r="F9" t="n" s="0">
+        <v>413700.0</v>
+      </c>
+      <c r="G9" t="n" s="0">
+        <v>469100.0</v>
+      </c>
+      <c r="H9" t="n" s="0">
+        <v>438700.0</v>
+      </c>
+      <c r="I9" t="n" s="0">
+        <v>437000.0</v>
+      </c>
+      <c r="J9" t="n" s="0">
+        <v>395700.0</v>
+      </c>
+      <c r="K9" t="n" s="0">
+        <v>377700.0</v>
+      </c>
+      <c r="L9" t="n" s="0">
+        <v>363800.0</v>
+      </c>
+      <c r="M9" t="n" s="0">
+        <v>468400.0</v>
+      </c>
+      <c r="N9" t="n" s="0">
+        <v>378400.0</v>
+      </c>
+      <c r="O9" t="n" s="0">
+        <v>451400.0</v>
+      </c>
+      <c r="P9" t="n" s="0">
+        <v>386300.0</v>
+      </c>
+      <c r="Q9" t="n" s="0">
+        <v>468200.0</v>
+      </c>
+      <c r="R9" t="n" s="0">
+        <v>454000.0</v>
+      </c>
+      <c r="S9" t="n" s="0">
+        <v>489700.0</v>
+      </c>
+      <c r="T9" t="n" s="0">
+        <v>424300.0</v>
+      </c>
+      <c r="U9" t="n" s="0">
+        <v>424200.0</v>
+      </c>
+      <c r="V9" t="n" s="0">
+        <v>494300.0</v>
+      </c>
+      <c r="W9" t="n" s="0">
+        <v>361200.0</v>
+      </c>
+      <c r="X9" t="n" s="0">
+        <v>403900.0</v>
+      </c>
+      <c r="Y9" t="n" s="0">
+        <v>395700.0</v>
+      </c>
+      <c r="Z9" t="n" s="0">
+        <v>378400.0</v>
+      </c>
+      <c r="AA9" t="n" s="0">
+        <v>408300.0</v>
+      </c>
+      <c r="AB9" t="n" s="0">
+        <v>396300.0</v>
+      </c>
+      <c r="AC9" t="n" s="0">
+        <v>361300.0</v>
+      </c>
+      <c r="AD9" t="n" s="0">
+        <v>488300.0</v>
+      </c>
+      <c r="AE9" t="n" s="0">
+        <v>381900.0</v>
+      </c>
+      <c r="AF9" t="n" s="0">
+        <v>408400.0</v>
+      </c>
+      <c r="AG9" t="n" s="0">
+        <v>470300.0</v>
+      </c>
+      <c r="AH9" t="n" s="0">
+        <v>452300.0</v>
+      </c>
+      <c r="AI9" t="n" s="0">
+        <v>377100.0</v>
+      </c>
+      <c r="AJ9" t="n" s="0">
+        <v>387900.0</v>
+      </c>
+      <c r="AK9" t="n" s="0">
+        <v>450200.0</v>
+      </c>
+      <c r="AL9" t="n" s="0">
+        <v>369800.0</v>
+      </c>
+      <c r="AM9" t="n" s="0">
+        <v>356100.0</v>
+      </c>
+      <c r="AN9" t="n" s="0">
+        <v>367500.0</v>
+      </c>
+      <c r="AO9" t="n" s="0">
+        <v>402000.0</v>
+      </c>
+      <c r="AP9" t="n" s="0">
+        <v>485500.0</v>
+      </c>
+      <c r="AQ9" t="n" s="0">
+        <v>520400.0</v>
+      </c>
+      <c r="AR9" t="n" s="0">
+        <v>445800.0</v>
+      </c>
+      <c r="AS9" t="n" s="0">
+        <v>539500.0</v>
+      </c>
+      <c r="AT9" t="n" s="0">
+        <v>432000.0</v>
+      </c>
+      <c r="AU9" t="n" s="0">
+        <v>428800.0</v>
+      </c>
+      <c r="AV9" t="n" s="0">
+        <v>444500.0</v>
+      </c>
+      <c r="AW9" t="n" s="0">
+        <v>1138500.0</v>
+      </c>
+      <c r="AX9" t="n" s="0">
+        <v>433400.0</v>
+      </c>
+      <c r="AY9" t="n" s="0">
+        <v>516300.0</v>
+      </c>
+      <c r="AZ9" t="n" s="0">
+        <v>436000.0</v>
+      </c>
+      <c r="BA9" t="n" s="0">
+        <v>457100.0</v>
+      </c>
+      <c r="BB9" t="n" s="0">
+        <v>434800.0</v>
+      </c>
+      <c r="BC9" t="n" s="0">
+        <v>361600.0</v>
+      </c>
+      <c r="BD9" t="n" s="0">
+        <v>353300.0</v>
+      </c>
+      <c r="BE9" t="n" s="0">
+        <v>377600.0</v>
+      </c>
+      <c r="BF9" t="n" s="0">
+        <v>367400.0</v>
+      </c>
+      <c r="BG9" t="n" s="0">
+        <v>374400.0</v>
+      </c>
+      <c r="BH9" t="n" s="0">
+        <v>371500.0</v>
+      </c>
+      <c r="BI9" t="n" s="0">
+        <v>366600.0</v>
+      </c>
+      <c r="BJ9" t="n" s="0">
+        <v>382000.0</v>
+      </c>
+      <c r="BK9" t="n" s="0">
+        <v>374500.0</v>
+      </c>
+      <c r="BL9" t="n" s="0">
+        <v>425600.0</v>
+      </c>
+      <c r="BM9" t="n" s="0">
+        <v>380100.0</v>
+      </c>
+      <c r="BN9" t="n" s="0">
+        <v>368300.0</v>
+      </c>
+      <c r="BO9" t="n" s="0">
+        <v>375700.0</v>
+      </c>
+      <c r="BP9" t="n" s="0">
+        <v>450400.0</v>
+      </c>
+      <c r="BQ9" t="n" s="0">
+        <v>375600.0</v>
+      </c>
+      <c r="BR9" t="n" s="0">
+        <v>390700.0</v>
+      </c>
+      <c r="BS9" t="n" s="0">
+        <v>404400.0</v>
+      </c>
+      <c r="BT9" t="n" s="0">
+        <v>361600.0</v>
+      </c>
+      <c r="BU9" t="n" s="0">
+        <v>349200.0</v>
+      </c>
+      <c r="BV9" t="n" s="0">
+        <v>363600.0</v>
+      </c>
+      <c r="BW9" t="n" s="0">
+        <v>371300.0</v>
+      </c>
+      <c r="BX9" t="n" s="0">
+        <v>427700.0</v>
+      </c>
+      <c r="BY9" t="n" s="0">
+        <v>2.6072E7</v>
+      </c>
+      <c r="BZ9" t="n" s="0">
+        <v>391500.0</v>
+      </c>
+      <c r="CA9" t="n" s="0">
+        <v>394300.0</v>
+      </c>
+      <c r="CB9" t="n" s="0">
+        <v>522000.0</v>
+      </c>
+      <c r="CC9" t="n" s="0">
+        <v>462300.0</v>
+      </c>
+      <c r="CD9" t="n" s="0">
+        <v>479600.0</v>
+      </c>
+      <c r="CE9" t="n" s="0">
+        <v>389600.0</v>
+      </c>
+      <c r="CF9" t="n" s="0">
+        <v>407400.0</v>
+      </c>
+      <c r="CG9" t="n" s="0">
+        <v>427900.0</v>
+      </c>
+      <c r="CH9" t="n" s="0">
+        <v>464500.0</v>
+      </c>
+      <c r="CI9" t="n" s="0">
+        <v>456400.0</v>
+      </c>
+      <c r="CJ9" t="n" s="0">
+        <v>473300.0</v>
+      </c>
+      <c r="CK9" t="n" s="0">
+        <v>439300.0</v>
+      </c>
+      <c r="CL9" t="n" s="0">
+        <v>447800.0</v>
+      </c>
+      <c r="CM9" t="n" s="0">
+        <v>448400.0</v>
+      </c>
+      <c r="CN9" t="n" s="0">
+        <v>433400.0</v>
+      </c>
+      <c r="CO9" t="n" s="0">
+        <v>850000.0</v>
+      </c>
+      <c r="CP9" t="n" s="0">
+        <v>495100.0</v>
+      </c>
+      <c r="CQ9" t="n" s="0">
+        <v>491100.0</v>
+      </c>
+      <c r="CR9" t="n" s="0">
+        <v>474400.0</v>
+      </c>
+      <c r="CS9" t="n" s="0">
+        <v>488700.0</v>
+      </c>
+      <c r="CT9" t="n" s="0">
+        <v>478700.0</v>
+      </c>
+      <c r="CU9" t="n" s="0">
+        <v>482900.0</v>
+      </c>
+      <c r="CV9" t="n" s="0">
+        <v>472400.0</v>
+      </c>
+      <c r="CW9" t="n" s="0">
+        <v>471800.0</v>
+      </c>
+      <c r="CX9" t="n" s="0">
+        <v>491300.0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="B10" t="n" s="0">
+        <v>5000.0</v>
+      </c>
+      <c r="C10" t="n" s="0">
+        <v>2075800.0</v>
+      </c>
+      <c r="D10" t="n" s="0">
+        <v>485900.0</v>
+      </c>
+      <c r="E10" t="n" s="0">
+        <v>606900.0</v>
+      </c>
+      <c r="F10" t="n" s="0">
+        <v>509400.0</v>
+      </c>
+      <c r="G10" t="n" s="0">
+        <v>615200.0</v>
+      </c>
+      <c r="H10" t="n" s="0">
+        <v>556400.0</v>
+      </c>
+      <c r="I10" t="n" s="0">
+        <v>570100.0</v>
+      </c>
+      <c r="J10" t="n" s="0">
+        <v>592100.0</v>
+      </c>
+      <c r="K10" t="n" s="0">
+        <v>460500.0</v>
+      </c>
+      <c r="L10" t="n" s="0">
+        <v>440500.0</v>
+      </c>
+      <c r="M10" t="n" s="0">
+        <v>605100.0</v>
+      </c>
+      <c r="N10" t="n" s="0">
+        <v>472500.0</v>
+      </c>
+      <c r="O10" t="n" s="0">
+        <v>584400.0</v>
+      </c>
+      <c r="P10" t="n" s="0">
+        <v>506600.0</v>
+      </c>
+      <c r="Q10" t="n" s="0">
+        <v>620200.0</v>
+      </c>
+      <c r="R10" t="n" s="0">
+        <v>955900.0</v>
+      </c>
+      <c r="S10" t="n" s="0">
+        <v>539000.0</v>
+      </c>
+      <c r="T10" t="n" s="0">
+        <v>585000.0</v>
+      </c>
+      <c r="U10" t="n" s="0">
+        <v>605900.0</v>
+      </c>
+      <c r="V10" t="n" s="0">
+        <v>606700.0</v>
+      </c>
+      <c r="W10" t="n" s="0">
+        <v>506500.0</v>
+      </c>
+      <c r="X10" t="n" s="0">
+        <v>467900.0</v>
+      </c>
+      <c r="Y10" t="n" s="0">
+        <v>479600.0</v>
+      </c>
+      <c r="Z10" t="n" s="0">
+        <v>489200.0</v>
+      </c>
+      <c r="AA10" t="n" s="0">
+        <v>486100.0</v>
+      </c>
+      <c r="AB10" t="n" s="0">
+        <v>454000.0</v>
+      </c>
+      <c r="AC10" t="n" s="0">
+        <v>448000.0</v>
+      </c>
+      <c r="AD10" t="n" s="0">
+        <v>589200.0</v>
+      </c>
+      <c r="AE10" t="n" s="0">
+        <v>441900.0</v>
+      </c>
+      <c r="AF10" t="n" s="0">
+        <v>518700.0</v>
+      </c>
+      <c r="AG10" t="n" s="0">
+        <v>619200.0</v>
+      </c>
+      <c r="AH10" t="n" s="0">
+        <v>549200.0</v>
+      </c>
+      <c r="AI10" t="n" s="0">
+        <v>499100.0</v>
+      </c>
+      <c r="AJ10" t="n" s="0">
+        <v>432000.0</v>
+      </c>
+      <c r="AK10" t="n" s="0">
+        <v>651900.0</v>
+      </c>
+      <c r="AL10" t="n" s="0">
+        <v>459900.0</v>
+      </c>
+      <c r="AM10" t="n" s="0">
+        <v>454200.0</v>
+      </c>
+      <c r="AN10" t="n" s="0">
+        <v>470400.0</v>
+      </c>
+      <c r="AO10" t="n" s="0">
+        <v>489700.0</v>
+      </c>
+      <c r="AP10" t="n" s="0">
+        <v>588300.0</v>
+      </c>
+      <c r="AQ10" t="n" s="0">
+        <v>631300.0</v>
+      </c>
+      <c r="AR10" t="n" s="0">
+        <v>576700.0</v>
+      </c>
+      <c r="AS10" t="n" s="0">
+        <v>592700.0</v>
+      </c>
+      <c r="AT10" t="n" s="0">
+        <v>560900.0</v>
+      </c>
+      <c r="AU10" t="n" s="0">
+        <v>561600.0</v>
+      </c>
+      <c r="AV10" t="n" s="0">
+        <v>584000.0</v>
+      </c>
+      <c r="AW10" t="n" s="0">
+        <v>581100.0</v>
+      </c>
+      <c r="AX10" t="n" s="0">
+        <v>571500.0</v>
+      </c>
+      <c r="AY10" t="n" s="0">
+        <v>543900.0</v>
+      </c>
+      <c r="AZ10" t="n" s="0">
+        <v>594600.0</v>
+      </c>
+      <c r="BA10" t="n" s="0">
+        <v>566800.0</v>
+      </c>
+      <c r="BB10" t="n" s="0">
+        <v>573300.0</v>
+      </c>
+      <c r="BC10" t="n" s="0">
+        <v>418200.0</v>
+      </c>
+      <c r="BD10" t="n" s="0">
+        <v>444300.0</v>
+      </c>
+      <c r="BE10" t="n" s="0">
+        <v>486100.0</v>
+      </c>
+      <c r="BF10" t="n" s="0">
+        <v>467200.0</v>
+      </c>
+      <c r="BG10" t="n" s="0">
+        <v>491700.0</v>
+      </c>
+      <c r="BH10" t="n" s="0">
+        <v>481100.0</v>
+      </c>
+      <c r="BI10" t="n" s="0">
+        <v>434000.0</v>
+      </c>
+      <c r="BJ10" t="n" s="0">
+        <v>505000.0</v>
+      </c>
+      <c r="BK10" t="n" s="0">
+        <v>475300.0</v>
+      </c>
+      <c r="BL10" t="n" s="0">
+        <v>444200.0</v>
+      </c>
+      <c r="BM10" t="n" s="0">
+        <v>531800.0</v>
+      </c>
+      <c r="BN10" t="n" s="0">
+        <v>443800.0</v>
+      </c>
+      <c r="BO10" t="n" s="0">
+        <v>504300.0</v>
+      </c>
+      <c r="BP10" t="n" s="0">
+        <v>558900.0</v>
+      </c>
+      <c r="BQ10" t="n" s="0">
+        <v>442100.0</v>
+      </c>
+      <c r="BR10" t="n" s="0">
+        <v>472000.0</v>
+      </c>
+      <c r="BS10" t="n" s="0">
+        <v>453000.0</v>
+      </c>
+      <c r="BT10" t="n" s="0">
+        <v>499900.0</v>
+      </c>
+      <c r="BU10" t="n" s="0">
+        <v>441100.0</v>
+      </c>
+      <c r="BV10" t="n" s="0">
+        <v>438100.0</v>
+      </c>
+      <c r="BW10" t="n" s="0">
+        <v>479400.0</v>
+      </c>
+      <c r="BX10" t="n" s="0">
+        <v>485000.0</v>
+      </c>
+      <c r="BY10" t="n" s="0">
+        <v>1033500.0</v>
+      </c>
+      <c r="BZ10" t="n" s="0">
+        <v>487700.0</v>
+      </c>
+      <c r="CA10" t="n" s="0">
+        <v>515500.0</v>
+      </c>
+      <c r="CB10" t="n" s="0">
+        <v>665600.0</v>
+      </c>
+      <c r="CC10" t="n" s="0">
+        <v>576000.0</v>
+      </c>
+      <c r="CD10" t="n" s="0">
+        <v>486100.0</v>
+      </c>
+      <c r="CE10" t="n" s="0">
+        <v>475200.0</v>
+      </c>
+      <c r="CF10" t="n" s="0">
+        <v>480000.0</v>
+      </c>
+      <c r="CG10" t="n" s="0">
+        <v>559000.0</v>
+      </c>
+      <c r="CH10" t="n" s="0">
+        <v>515900.0</v>
+      </c>
+      <c r="CI10" t="n" s="0">
+        <v>595500.0</v>
+      </c>
+      <c r="CJ10" t="n" s="0">
+        <v>552100.0</v>
+      </c>
+      <c r="CK10" t="n" s="0">
+        <v>583400.0</v>
+      </c>
+      <c r="CL10" t="n" s="0">
+        <v>558700.0</v>
+      </c>
+      <c r="CM10" t="n" s="0">
+        <v>609500.0</v>
+      </c>
+      <c r="CN10" t="n" s="0">
+        <v>555900.0</v>
+      </c>
+      <c r="CO10" t="n" s="0">
+        <v>958400.0</v>
+      </c>
+      <c r="CP10" t="n" s="0">
+        <v>601100.0</v>
+      </c>
+      <c r="CQ10" t="n" s="0">
+        <v>581600.0</v>
+      </c>
+      <c r="CR10" t="n" s="0">
+        <v>615800.0</v>
+      </c>
+      <c r="CS10" t="n" s="0">
+        <v>641300.0</v>
+      </c>
+      <c r="CT10" t="n" s="0">
+        <v>669000.0</v>
+      </c>
+      <c r="CU10" t="n" s="0">
+        <v>635000.0</v>
+      </c>
+      <c r="CV10" t="n" s="0">
+        <v>596700.0</v>
+      </c>
+      <c r="CW10" t="n" s="0">
+        <v>699800.0</v>
+      </c>
+      <c r="CX10" t="n" s="0">
+        <v>590000.0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="B11" t="n" s="0">
+        <v>5000.0</v>
+      </c>
+      <c r="C11" t="n" s="0">
+        <v>1913600.0</v>
+      </c>
+      <c r="D11" t="n" s="0">
+        <v>467900.0</v>
+      </c>
+      <c r="E11" t="n" s="0">
+        <v>596500.0</v>
+      </c>
+      <c r="F11" t="n" s="0">
+        <v>491800.0</v>
+      </c>
+      <c r="G11" t="n" s="0">
+        <v>616800.0</v>
+      </c>
+      <c r="H11" t="n" s="0">
+        <v>599500.0</v>
+      </c>
+      <c r="I11" t="n" s="0">
+        <v>1.2781E7</v>
+      </c>
+      <c r="J11" t="n" s="0">
+        <v>503900.0</v>
+      </c>
+      <c r="K11" t="n" s="0">
+        <v>1.76004E7</v>
+      </c>
+      <c r="L11" t="n" s="0">
+        <v>480600.0</v>
+      </c>
+      <c r="M11" t="n" s="0">
+        <v>614600.0</v>
+      </c>
+      <c r="N11" t="n" s="0">
+        <v>539700.0</v>
+      </c>
+      <c r="O11" t="n" s="0">
+        <v>554400.0</v>
+      </c>
+      <c r="P11" t="n" s="0">
+        <v>519300.0</v>
+      </c>
+      <c r="Q11" t="n" s="0">
+        <v>680300.0</v>
+      </c>
+      <c r="R11" t="n" s="0">
+        <v>628000.0</v>
+      </c>
+      <c r="S11" t="n" s="0">
+        <v>582500.0</v>
+      </c>
+      <c r="T11" t="n" s="0">
+        <v>536800.0</v>
+      </c>
+      <c r="U11" t="n" s="0">
+        <v>541800.0</v>
+      </c>
+      <c r="V11" t="n" s="0">
+        <v>553400.0</v>
+      </c>
+      <c r="W11" t="n" s="0">
+        <v>554800.0</v>
+      </c>
+      <c r="X11" t="n" s="0">
+        <v>517100.0</v>
+      </c>
+      <c r="Y11" t="n" s="0">
+        <v>503200.0</v>
+      </c>
+      <c r="Z11" t="n" s="0">
+        <v>555500.0</v>
+      </c>
+      <c r="AA11" t="n" s="0">
+        <v>517300.0</v>
+      </c>
+      <c r="AB11" t="n" s="0">
+        <v>506200.0</v>
+      </c>
+      <c r="AC11" t="n" s="0">
+        <v>488900.0</v>
+      </c>
+      <c r="AD11" t="n" s="0">
+        <v>579700.0</v>
+      </c>
+      <c r="AE11" t="n" s="0">
+        <v>478100.0</v>
+      </c>
+      <c r="AF11" t="n" s="0">
+        <v>496400.0</v>
+      </c>
+      <c r="AG11" t="n" s="0">
+        <v>579800.0</v>
+      </c>
+      <c r="AH11" t="n" s="0">
+        <v>605000.0</v>
+      </c>
+      <c r="AI11" t="n" s="0">
+        <v>504300.0</v>
+      </c>
+      <c r="AJ11" t="n" s="0">
+        <v>487000.0</v>
+      </c>
+      <c r="AK11" t="n" s="0">
+        <v>635600.0</v>
+      </c>
+      <c r="AL11" t="n" s="0">
+        <v>481100.0</v>
+      </c>
+      <c r="AM11" t="n" s="0">
+        <v>546700.0</v>
+      </c>
+      <c r="AN11" t="n" s="0">
+        <v>509800.0</v>
+      </c>
+      <c r="AO11" t="n" s="0">
+        <v>526500.0</v>
+      </c>
+      <c r="AP11" t="n" s="0">
+        <v>655500.0</v>
+      </c>
+      <c r="AQ11" t="n" s="0">
+        <v>715500.0</v>
+      </c>
+      <c r="AR11" t="n" s="0">
+        <v>567200.0</v>
+      </c>
+      <c r="AS11" t="n" s="0">
+        <v>584200.0</v>
+      </c>
+      <c r="AT11" t="n" s="0">
+        <v>609900.0</v>
+      </c>
+      <c r="AU11" t="n" s="0">
+        <v>612600.0</v>
+      </c>
+      <c r="AV11" t="n" s="0">
+        <v>555600.0</v>
+      </c>
+      <c r="AW11" t="n" s="0">
+        <v>589900.0</v>
+      </c>
+      <c r="AX11" t="n" s="0">
+        <v>624800.0</v>
+      </c>
+      <c r="AY11" t="n" s="0">
+        <v>573000.0</v>
+      </c>
+      <c r="AZ11" t="n" s="0">
+        <v>682100.0</v>
+      </c>
+      <c r="BA11" t="n" s="0">
+        <v>535600.0</v>
+      </c>
+      <c r="BB11" t="n" s="0">
+        <v>5.51871E7</v>
+      </c>
+      <c r="BC11" t="n" s="0">
+        <v>467900.0</v>
+      </c>
+      <c r="BD11" t="n" s="0">
+        <v>483100.0</v>
+      </c>
+      <c r="BE11" t="n" s="0">
+        <v>503000.0</v>
+      </c>
+      <c r="BF11" t="n" s="0">
+        <v>460000.0</v>
+      </c>
+      <c r="BG11" t="n" s="0">
+        <v>519400.0</v>
+      </c>
+      <c r="BH11" t="n" s="0">
+        <v>501600.0</v>
+      </c>
+      <c r="BI11" t="n" s="0">
+        <v>488400.0</v>
+      </c>
+      <c r="BJ11" t="n" s="0">
+        <v>446000.0</v>
+      </c>
+      <c r="BK11" t="n" s="0">
+        <v>505300.0</v>
+      </c>
+      <c r="BL11" t="n" s="0">
+        <v>498200.0</v>
+      </c>
+      <c r="BM11" t="n" s="0">
+        <v>510900.0</v>
+      </c>
+      <c r="BN11" t="n" s="0">
+        <v>488700.0</v>
+      </c>
+      <c r="BO11" t="n" s="0">
+        <v>526400.0</v>
+      </c>
+      <c r="BP11" t="n" s="0">
+        <v>540100.0</v>
+      </c>
+      <c r="BQ11" t="n" s="0">
+        <v>479000.0</v>
+      </c>
+      <c r="BR11" t="n" s="0">
+        <v>425700.0</v>
+      </c>
+      <c r="BS11" t="n" s="0">
+        <v>485100.0</v>
+      </c>
+      <c r="BT11" t="n" s="0">
+        <v>433400.0</v>
+      </c>
+      <c r="BU11" t="n" s="0">
+        <v>488200.0</v>
+      </c>
+      <c r="BV11" t="n" s="0">
+        <v>487200.0</v>
+      </c>
+      <c r="BW11" t="n" s="0">
+        <v>514100.0</v>
+      </c>
+      <c r="BX11" t="n" s="0">
+        <v>542300.0</v>
+      </c>
+      <c r="BY11" t="n" s="0">
+        <v>546200.0</v>
+      </c>
+      <c r="BZ11" t="n" s="0">
+        <v>583500.0</v>
+      </c>
+      <c r="CA11" t="n" s="0">
+        <v>580800.0</v>
+      </c>
+      <c r="CB11" t="n" s="0">
+        <v>695600.0</v>
+      </c>
+      <c r="CC11" t="n" s="0">
+        <v>643300.0</v>
+      </c>
+      <c r="CD11" t="n" s="0">
+        <v>471900.0</v>
+      </c>
+      <c r="CE11" t="n" s="0">
+        <v>531200.0</v>
+      </c>
+      <c r="CF11" t="n" s="0">
+        <v>520600.0</v>
+      </c>
+      <c r="CG11" t="n" s="0">
+        <v>552500.0</v>
+      </c>
+      <c r="CH11" t="n" s="0">
+        <v>586900.0</v>
+      </c>
+      <c r="CI11" t="n" s="0">
+        <v>582700.0</v>
+      </c>
+      <c r="CJ11" t="n" s="0">
+        <v>544000.0</v>
+      </c>
+      <c r="CK11" t="n" s="0">
+        <v>677100.0</v>
+      </c>
+      <c r="CL11" t="n" s="0">
+        <v>625100.0</v>
+      </c>
+      <c r="CM11" t="n" s="0">
+        <v>578100.0</v>
+      </c>
+      <c r="CN11" t="n" s="0">
+        <v>542900.0</v>
+      </c>
+      <c r="CO11" t="n" s="0">
+        <v>1068000.0</v>
+      </c>
+      <c r="CP11" t="n" s="0">
+        <v>609100.0</v>
+      </c>
+      <c r="CQ11" t="n" s="0">
+        <v>595000.0</v>
+      </c>
+      <c r="CR11" t="n" s="0">
+        <v>569000.0</v>
+      </c>
+      <c r="CS11" t="n" s="0">
+        <v>612000.0</v>
+      </c>
+      <c r="CT11" t="n" s="0">
+        <v>580100.0</v>
+      </c>
+      <c r="CU11" t="n" s="0">
+        <v>671400.0</v>
+      </c>
+      <c r="CV11" t="n" s="0">
+        <v>664600.0</v>
+      </c>
+      <c r="CW11" t="n" s="0">
+        <v>632800.0</v>
+      </c>
+      <c r="CX11" t="n" s="0">
+        <v>639100.0</v>
       </c>
     </row>
   </sheetData>
